--- a/documentación/PRSC/Dailys.xlsx
+++ b/documentación/PRSC/Dailys.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="903" uniqueCount="233">
   <si>
     <t xml:space="preserve">Daily</t>
   </si>
@@ -46,190 +46,679 @@
     <t xml:space="preserve">Santiago Centurion</t>
   </si>
   <si>
-    <t xml:space="preserve">Devloper </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plastificado de tarjetas</t>
+    <t xml:space="preserve">Devloper</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crear la carpeta del proyecto</t>
   </si>
   <si>
     <t xml:space="preserve">Finalizada</t>
   </si>
   <si>
-    <t xml:space="preserve">Lorenzo Sanchez </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Base de datos </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hacer el MER</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valentin Lopez </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Proyect manager </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Creacion de github</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sistema de gestion remiseria casablanca</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Santino Tacconi </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Creacion de logo del proyecto </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hacer el MR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Creacion del KANBAN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Formulario del proyecto </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estudio de factibilidad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Completar la plantilla de lista de tareas </t>
+    <t xml:space="preserve">Lorenzo Sanchez</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Base de datos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Disenar el MER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valentin Lopez</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Proyect manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Armar el GANTT</t>
   </si>
   <si>
     <t xml:space="preserve">En Proceso</t>
   </si>
   <si>
-    <t xml:space="preserve">Completar la plantilla de acta de reunion </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Completar la plantilla de proyect charter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Creacion de microempredimiento</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Carta de solucitud del proyecto </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Entrevistas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Analisis Factibilidad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Proyección y justificación del sistema</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Analisis FODA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Creación y justificación del ambiente de desarrollo y producción</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Creacion de GANTT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bruno cabrera</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Diseño UX </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Resultado del formulario</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Primera entrega funcional</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lorenzo Sanchez Y Bruno cabrera</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Base de datos Y Diseño UX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UML del proyecto </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Historias de usuarios.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Base da datos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">correcion UML</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pantallas/mockups</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tipos de datos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gama de colores de las pantallas/mockups</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elección de arquitectura del proyecto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bada</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Creacion del SQL de la base de datos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pantallas avance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Presupuesto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Diagrama de contexto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DFD 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DFD 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pantallas AMB usuario</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Creacion del backend</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Creacion de querys</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Testing de la pagina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Testing de la recuperar contraseña</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pantallas de favoritos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deploy de proyecto en render</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Subir el codigo a github</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arreglos en render de enviroment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Agregar brevo el render</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Conexion supabe al proyecto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verificar el funcionameinto de recuperar contraseña</t>
+    <t xml:space="preserve">Bruno Cabrera</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diseño UX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dibujar los wireframes</t>
   </si>
   <si>
     <t xml:space="preserve">Proceso</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Instalar lo que necesita el proyecto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Armar el MR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Definir el alcance del proyecto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Definir los colores</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Organizar las carpetas del codigo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Escribir el diccionario de datos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hacer entrevistas a usuarios</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elegir la paleta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Levantar el proyecto base</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dibujar el DER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hacer la encuesta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hacer los mockups</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Configurar los programas del proyecto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Definir las tablas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Juntar los resultados</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elegir las letras</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crear el repositorio en github</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revisar las relaciones</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hacer el estudio de factibilidad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hacer el prototipo en papel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Probar que arranque el proyecto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elegir el motor de base de datos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calcular el presupuesto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Disenar el onboarding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leer la consigna del proyecto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Escribir las politicas de datos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Justificar el stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anotar decisiones de diseno</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anotar las ideas del equipo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revisar el modelo con el equipo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pensar el impacto del sistema</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Disenar los flujos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crear la estructura del backend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Escribir el DDL de la base</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revisar los requisitos del backend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mejorar la card de cotizacion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conectar la base de datos al backend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crear la tabla usuarios</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coordinar con las APIs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Disenar login y registro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hacer el registro de usuarios</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crear la tabla divisas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Actualizar el GANTT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dibujar el flujo de recuperar contrasena</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hacer el login</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crear la tabla tipos de cambio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Documentar la API</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Disenar el dashboard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Proteger las rutas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crear la tabla favoritos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Probar los endpoints</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elegir colores para las variaciones</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conectar la API del dolar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crear la tabla historial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Organizar el trabajo del grupo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Disenar el formulario</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conectar la API de criptos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crear la tabla notificaciones</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anotar decisiones tecnicas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hacer componentes reutilizables</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crear el endpoint de cotizaciones</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crear la tabla acciones bursatiles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Controlar los plazos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Disenar la calculadora</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Guardar las cotizaciones en cache</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agregar indices</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preparar el deploy en Render</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Disenar el grafico</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Programar la actualizacion automatica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cargar datos de prueba</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Organizar los ambientes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Disenar la vista de favoritos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Probar el recuperar contrasena</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crear las vistas de cotizaciones</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Escribir el manual de la API</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Disenar estados vacios</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crear el endpoint del historial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Probar la integridad de los datos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coordinar pruebas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hacer las pantallas AMB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crear el CRUD de favoritos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimizar las consultas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Definir la seguridad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Disenar el panel de bolsa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crear el endpoint de conversion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anotar como hacer las migraciones</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anotar las pruebas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Disenar los avisos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conectar los datos de bolsa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hacer las migraciones nuevas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revisar los emails</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Disenar los emails</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crear las notificaciones</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conectar Supabase</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Configurar Render</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Probar la usabilidad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Probar todos los endpoints</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revisar los permisos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ajustar las maquetas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crear el proyecto con Vite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hacer las consultas del dashboard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Organizar el sprint del front</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mejorar el dashboard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Configurar las rutas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hacer las consultas del historial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hacer la version mobile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Guardar el login en el contexto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimizar favoritos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revisar el dashboard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hacer la navegacion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hacer la pagina de registro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Guardar consultas frecuentes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coordinar reuniones</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Disenar la configuracion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hacer la pagina de login</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Probar el historial desde la web</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Escribir el manual de usuario</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hacer el selector de moneda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cargar mas datos de prueba</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revisar las pantallas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terminar la card de cotizacion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Armar el dashboard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revisar que las vistas muestren bien</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anotar la reunion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agregar animaciones</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agregar filtros al dashboard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crear indices nuevos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coordinar front y back</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Probar en el celular</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ordenar las cotizaciones</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ajustar los tipos de cambio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preparar el deploy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hacer la vista de favoritos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Armar la card de cotizacion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agregar las monedas del mundo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revisar la presentacion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hacer la calculadora</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Consultar criptos para el dashboard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Juntar feedback del equipo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Redisenar recuperar contrasena</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agregar el grafico con Chart.js</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arreglar las fechas del historial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Actualizar la documentacion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terminar el grafico</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mostrar favoritos en la web</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revisar los datos de bolsa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revisar el GANTT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hacer componentes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hacer la pagina de favoritos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arreglar la tabla de tipos de cambio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Probar favoritos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hacer la pagina de historial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Probar la sincronizacion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anotar el testing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hacer el prototipo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Armar la seccion de bolsa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revisar las cotizaciones activas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Organizar la demo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Refrescar las cotizaciones solas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Analizar consultas lentas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revisar requisitos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revisar colores y letras</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mostrar mensajes de carga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hacer un respaldo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preparar la entrega</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hacer los graficos del proyecto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agregar boton para compartir</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Documentar los errores</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mostrar avisos en la pagina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revisar los emails de Brevo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terminar los emails</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mostrar la ultima actualizacion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revisar la seguridad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control general</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Probar con un usuario</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hacer la pagina de recuperar contrasena</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Borrar datos de prueba</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Actualizar actas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revisar la accesibilidad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arreglar los mensajes de error</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verificar que se guarde el historial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revisar el presupuesto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hacer el prototipo en Figma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arreglar la conexion con el front</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimizar consultas otra vez</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Armar las slides</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terminar la guia de estilos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Probar los endpoints de nuevo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Probar integridad de nuevo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Organizar la demo final</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revisar estados vacios</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arreglar errores que saltan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revisar los permisos de Supabase</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cerrar el GANTT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revisar la identidad visual</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corregir el codigo de cotizaciones</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revisar los precios de criptos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Actualizar el GANTT final</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revisar el visual del historial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arreglar lo de la redireccion del historial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pasar los precios a ARS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anotar las correcciones</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ajustar la UI de recuperar contrasena</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arreglar el recuperar contrasena</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confirmar datos de CAD y AUD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Juntar la carpeta final</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revisar los graficos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preparar la demo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Probar la sincronizacion final</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entregar la demo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aprobar la demo</t>
   </si>
 </sst>
 </file>
@@ -239,7 +728,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="7">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -284,19 +773,6 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <name val="Cambria"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -318,7 +794,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="2">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -328,20 +804,6 @@
     </border>
     <border diagonalUp="false" diagonalDown="false">
       <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left/>
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
@@ -373,7 +835,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="9">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -407,18 +869,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -502,37 +952,37 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
+        <a:srgbClr val="ffffff"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="FFFFFF"/>
+        <a:srgbClr val="ffffff"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4285F4"/>
+        <a:srgbClr val="4285f4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="EA4335"/>
+        <a:srgbClr val="ea4335"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="FBBC04"/>
+        <a:srgbClr val="fbbc04"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="34A853"/>
+        <a:srgbClr val="34a853"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="FF6D01"/>
+        <a:srgbClr val="ff6d01"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="46BDC6"/>
+        <a:srgbClr val="46bdc6"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="1155CC"/>
+        <a:srgbClr val="1155cc"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="1155CC"/>
+        <a:srgbClr val="1155cc"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Sheets">
@@ -671,8 +1121,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A2:GC195"/>
-  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A2:GC227"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="18.92"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="19.33"/>
@@ -893,7 +1343,7 @@
         <v>8</v>
       </c>
       <c r="D4" s="8" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E4" s="8" t="n">
         <v>4</v>
@@ -916,7 +1366,7 @@
         <v>12</v>
       </c>
       <c r="D5" s="8" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="E5" s="8" t="n">
         <v>4</v>
@@ -939,7 +1389,7 @@
         <v>15</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="E6" s="8" t="n">
         <v>4</v>
@@ -951,53 +1401,53 @@
       <c r="H6" s="8"/>
       <c r="I6" s="8"/>
       <c r="J6" s="8" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="7" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="E7" s="8" t="n">
         <v>4</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G7" s="8"/>
       <c r="H7" s="8"/>
       <c r="I7" s="8"/>
       <c r="J7" s="8" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="7" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="C8" s="7" t="s">
         <v>8</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="E8" s="8" t="n">
         <v>4</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G8" s="8"/>
       <c r="H8" s="8"/>
       <c r="I8" s="8"/>
       <c r="J8" s="8" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1008,13 +1458,13 @@
         <v>12</v>
       </c>
       <c r="D9" s="8" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="E9" s="8" t="n">
         <v>4</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G9" s="8"/>
       <c r="H9" s="8"/>
@@ -1031,13 +1481,13 @@
         <v>15</v>
       </c>
       <c r="D10" s="8" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="E10" s="8" t="n">
         <v>4</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G10" s="8"/>
       <c r="H10" s="8"/>
@@ -1048,42 +1498,42 @@
     </row>
     <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="7" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D11" s="8" t="n">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="E11" s="8" t="n">
         <v>4</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="G11" s="9"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="10"/>
+        <v>25</v>
+      </c>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="8"/>
       <c r="J11" s="8" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="7" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D12" s="8" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="E12" s="8" t="n">
         <v>4</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G12" s="8"/>
       <c r="H12" s="8"/>
@@ -1094,25 +1544,25 @@
     </row>
     <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="7" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D13" s="8" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="E13" s="8" t="n">
         <v>4</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G13" s="8"/>
       <c r="H13" s="8"/>
       <c r="I13" s="8"/>
       <c r="J13" s="8" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1123,19 +1573,19 @@
         <v>15</v>
       </c>
       <c r="D14" s="8" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="E14" s="8" t="n">
         <v>4</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G14" s="8"/>
       <c r="H14" s="8"/>
       <c r="I14" s="8"/>
       <c r="J14" s="8" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1143,39 +1593,39 @@
         <v>18</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D15" s="8" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="E15" s="8" t="n">
         <v>4</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G15" s="8"/>
       <c r="H15" s="8"/>
       <c r="I15" s="8"/>
       <c r="J15" s="8" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="7" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D16" s="8" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E16" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G16" s="8"/>
       <c r="H16" s="8"/>
@@ -1186,19 +1636,19 @@
     </row>
     <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="7" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D17" s="8" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E17" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G17" s="8"/>
       <c r="H17" s="8"/>
@@ -1215,13 +1665,13 @@
         <v>15</v>
       </c>
       <c r="D18" s="8" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E18" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G18" s="8"/>
       <c r="H18" s="8"/>
@@ -1232,19 +1682,19 @@
     </row>
     <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="7" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D19" s="8" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E19" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G19" s="8"/>
       <c r="H19" s="8"/>
@@ -1255,19 +1705,19 @@
     </row>
     <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="7" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D20" s="8" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G20" s="8"/>
       <c r="H20" s="8"/>
@@ -1278,19 +1728,19 @@
     </row>
     <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="7" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D21" s="8" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G21" s="8"/>
       <c r="H21" s="8"/>
@@ -1307,13 +1757,13 @@
         <v>15</v>
       </c>
       <c r="D22" s="8" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G22" s="8"/>
       <c r="H22" s="8"/>
@@ -1324,19 +1774,19 @@
     </row>
     <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="7" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="D23" s="8" t="n">
+        <v>16</v>
+      </c>
+      <c r="E23" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="E23" s="8" t="n">
-        <v>5</v>
-      </c>
       <c r="F23" s="8" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G23" s="8"/>
       <c r="H23" s="8"/>
@@ -1347,16 +1797,16 @@
     </row>
     <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="7" t="s">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="D24" s="8" t="n">
+        <v>17</v>
+      </c>
+      <c r="E24" s="8" t="n">
         <v>4</v>
-      </c>
-      <c r="E24" s="8" t="n">
-        <v>5</v>
       </c>
       <c r="F24" s="8" t="s">
         <v>38</v>
@@ -1370,16 +1820,16 @@
     </row>
     <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="7" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D25" s="8" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="E25" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F25" s="8" t="s">
         <v>39</v>
@@ -1388,24 +1838,24 @@
       <c r="H25" s="8"/>
       <c r="I25" s="8"/>
       <c r="J25" s="8" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D26" s="8" t="n">
+        <v>17</v>
+      </c>
+      <c r="E26" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="F26" s="8" t="s">
         <v>40</v>
-      </c>
-      <c r="C26" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="D26" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="E26" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="F26" s="8" t="s">
-        <v>42</v>
       </c>
       <c r="G26" s="8"/>
       <c r="H26" s="8"/>
@@ -1415,43 +1865,43 @@
       </c>
     </row>
     <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C27" s="8" t="s">
-        <v>15</v>
+      <c r="B27" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>19</v>
       </c>
       <c r="D27" s="8" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E27" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G27" s="8"/>
       <c r="H27" s="8"/>
       <c r="I27" s="8"/>
       <c r="J27" s="8" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="8" t="s">
-        <v>44</v>
+      <c r="B28" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>8</v>
       </c>
       <c r="D28" s="8" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E28" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F28" s="8" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G28" s="8"/>
       <c r="H28" s="8"/>
@@ -1461,20 +1911,20 @@
       </c>
     </row>
     <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C29" s="8" t="s">
-        <v>15</v>
+      <c r="B29" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="D29" s="8" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E29" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="G29" s="8"/>
       <c r="H29" s="8"/>
@@ -1484,43 +1934,43 @@
       </c>
     </row>
     <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="11" t="s">
+      <c r="B30" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C30" s="8" t="s">
+      <c r="C30" s="7" t="s">
         <v>15</v>
       </c>
       <c r="D30" s="8" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E30" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F30" s="8" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G30" s="8"/>
       <c r="H30" s="8"/>
       <c r="I30" s="8"/>
       <c r="J30" s="8" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C31" s="8" t="s">
-        <v>15</v>
+      <c r="B31" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>19</v>
       </c>
       <c r="D31" s="8" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E31" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F31" s="8" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="G31" s="8"/>
       <c r="H31" s="8"/>
@@ -1530,20 +1980,20 @@
       </c>
     </row>
     <row r="32" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B32" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C32" s="8" t="s">
-        <v>15</v>
+      <c r="B32" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>8</v>
       </c>
       <c r="D32" s="8" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E32" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G32" s="8"/>
       <c r="H32" s="8"/>
@@ -1553,20 +2003,20 @@
       </c>
     </row>
     <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="8" t="s">
+      <c r="B33" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C33" s="8" t="s">
-        <v>50</v>
+      <c r="C33" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="D33" s="8" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="E33" s="8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F33" s="8" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G33" s="8"/>
       <c r="H33" s="8"/>
@@ -1576,20 +2026,20 @@
       </c>
     </row>
     <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B34" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="C34" s="8" t="s">
-        <v>37</v>
+      <c r="B34" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>15</v>
       </c>
       <c r="D34" s="8" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E34" s="8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G34" s="8"/>
       <c r="H34" s="8"/>
@@ -1599,20 +2049,20 @@
       </c>
     </row>
     <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B35" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="C35" s="8" t="s">
-        <v>15</v>
+      <c r="B35" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>19</v>
       </c>
       <c r="D35" s="8" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="E35" s="8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G35" s="8"/>
       <c r="H35" s="8"/>
@@ -1622,20 +2072,20 @@
       </c>
     </row>
     <row r="36" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B36" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="C36" s="8" t="s">
-        <v>15</v>
+      <c r="B36" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>8</v>
       </c>
       <c r="D36" s="8" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="E36" s="8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F36" s="8" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="G36" s="8"/>
       <c r="H36" s="8"/>
@@ -1645,20 +2095,20 @@
       </c>
     </row>
     <row r="37" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B37" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="C37" s="8" t="s">
-        <v>15</v>
+      <c r="B37" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="D37" s="8" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="E37" s="8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F37" s="8" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="G37" s="8"/>
       <c r="H37" s="8"/>
@@ -1668,20 +2118,20 @@
       </c>
     </row>
     <row r="38" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B38" s="8" t="s">
+      <c r="B38" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C38" s="8" t="s">
+      <c r="C38" s="7" t="s">
         <v>15</v>
       </c>
       <c r="D38" s="8" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="E38" s="8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F38" s="8" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="G38" s="8"/>
       <c r="H38" s="8"/>
@@ -1691,20 +2141,20 @@
       </c>
     </row>
     <row r="39" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B39" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="C39" s="8" t="s">
-        <v>15</v>
+      <c r="B39" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C39" s="7" t="s">
+        <v>19</v>
       </c>
       <c r="D39" s="8" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="E39" s="8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F39" s="8" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G39" s="8"/>
       <c r="H39" s="8"/>
@@ -1714,20 +2164,20 @@
       </c>
     </row>
     <row r="40" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B40" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C40" s="8" t="s">
+      <c r="B40" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C40" s="7" t="s">
         <v>8</v>
       </c>
       <c r="D40" s="8" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="E40" s="8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F40" s="8" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="G40" s="8"/>
       <c r="H40" s="8"/>
@@ -1737,20 +2187,20 @@
       </c>
     </row>
     <row r="41" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B41" s="8" t="s">
+      <c r="B41" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C41" s="8" t="s">
-        <v>50</v>
+      <c r="C41" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="D41" s="8" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="E41" s="8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F41" s="8" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G41" s="8"/>
       <c r="H41" s="8"/>
@@ -1760,20 +2210,20 @@
       </c>
     </row>
     <row r="42" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B42" s="8" t="s">
+      <c r="B42" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C42" s="8" t="s">
+      <c r="C42" s="7" t="s">
         <v>15</v>
       </c>
       <c r="D42" s="8" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="E42" s="8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F42" s="8" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="G42" s="8"/>
       <c r="H42" s="8"/>
@@ -1783,20 +2233,20 @@
       </c>
     </row>
     <row r="43" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B43" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="C43" s="8" t="s">
-        <v>15</v>
+      <c r="B43" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C43" s="7" t="s">
+        <v>19</v>
       </c>
       <c r="D43" s="8" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="E43" s="8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F43" s="8" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="G43" s="8"/>
       <c r="H43" s="8"/>
@@ -1806,43 +2256,43 @@
       </c>
     </row>
     <row r="44" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B44" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="C44" s="8" t="s">
-        <v>37</v>
+      <c r="B44" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C44" s="7" t="s">
+        <v>8</v>
       </c>
       <c r="D44" s="8" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E44" s="8" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F44" s="8" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="G44" s="8"/>
       <c r="H44" s="8"/>
       <c r="I44" s="8"/>
       <c r="J44" s="8" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B45" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C45" s="8" t="s">
-        <v>8</v>
+      <c r="B45" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C45" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="D45" s="8" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E45" s="8" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F45" s="8" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="G45" s="8"/>
       <c r="H45" s="8"/>
@@ -1852,20 +2302,20 @@
       </c>
     </row>
     <row r="46" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B46" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C46" s="8" t="s">
-        <v>8</v>
+      <c r="B46" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C46" s="7" t="s">
+        <v>15</v>
       </c>
       <c r="D46" s="8" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="E46" s="8" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F46" s="8" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="G46" s="8"/>
       <c r="H46" s="8"/>
@@ -1875,20 +2325,20 @@
       </c>
     </row>
     <row r="47" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B47" s="8" t="s">
+      <c r="B47" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C47" s="8" t="s">
-        <v>8</v>
+      <c r="C47" s="7" t="s">
+        <v>19</v>
       </c>
       <c r="D47" s="8" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="E47" s="8" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F47" s="8" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G47" s="8"/>
       <c r="H47" s="8"/>
@@ -1898,20 +2348,20 @@
       </c>
     </row>
     <row r="48" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B48" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="C48" s="8" t="s">
-        <v>15</v>
+      <c r="B48" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C48" s="7" t="s">
+        <v>8</v>
       </c>
       <c r="D48" s="8" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="E48" s="8" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F48" s="8" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="G48" s="8"/>
       <c r="H48" s="8"/>
@@ -1921,1635 +2371,4121 @@
       </c>
     </row>
     <row r="49" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B49" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="C49" s="8" t="s">
-        <v>15</v>
+      <c r="B49" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C49" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="D49" s="8" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="E49" s="8" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F49" s="8" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="G49" s="8"/>
       <c r="H49" s="8"/>
       <c r="I49" s="8"/>
       <c r="J49" s="8" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B50" s="8" t="s">
+      <c r="B50" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C50" s="8" t="s">
+      <c r="C50" s="7" t="s">
         <v>15</v>
       </c>
       <c r="D50" s="8" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="E50" s="8" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F50" s="8" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="G50" s="8"/>
       <c r="H50" s="8"/>
       <c r="I50" s="8"/>
       <c r="J50" s="8" t="s">
-        <v>69</v>
+        <v>10</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B51" s="8"/>
-      <c r="C51" s="8"/>
-      <c r="D51" s="8"/>
-      <c r="E51" s="8"/>
-      <c r="F51" s="8"/>
+      <c r="B51" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C51" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D51" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="E51" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F51" s="8" t="s">
+        <v>65</v>
+      </c>
       <c r="G51" s="8"/>
       <c r="H51" s="8"/>
       <c r="I51" s="8"/>
-      <c r="J51" s="8"/>
+      <c r="J51" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="52" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B52" s="8"/>
-      <c r="C52" s="8"/>
-      <c r="D52" s="8"/>
-      <c r="E52" s="8"/>
-      <c r="F52" s="8"/>
+      <c r="B52" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C52" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D52" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="E52" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F52" s="8" t="s">
+        <v>66</v>
+      </c>
       <c r="G52" s="8"/>
       <c r="H52" s="8"/>
       <c r="I52" s="8"/>
-      <c r="J52" s="8"/>
+      <c r="J52" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="53" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B53" s="8"/>
-      <c r="C53" s="8"/>
-      <c r="D53" s="8"/>
-      <c r="E53" s="8"/>
-      <c r="F53" s="8"/>
+      <c r="B53" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C53" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D53" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="E53" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F53" s="8" t="s">
+        <v>67</v>
+      </c>
       <c r="G53" s="8"/>
       <c r="H53" s="8"/>
       <c r="I53" s="8"/>
-      <c r="J53" s="8"/>
+      <c r="J53" s="8" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="54" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B54" s="8"/>
-      <c r="C54" s="8"/>
-      <c r="D54" s="8"/>
-      <c r="E54" s="8"/>
-      <c r="F54" s="8"/>
+      <c r="B54" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C54" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D54" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="E54" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F54" s="8" t="s">
+        <v>68</v>
+      </c>
       <c r="G54" s="8"/>
       <c r="H54" s="8"/>
       <c r="I54" s="8"/>
-      <c r="J54" s="8"/>
+      <c r="J54" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="55" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B55" s="8"/>
-      <c r="C55" s="8"/>
-      <c r="D55" s="8"/>
-      <c r="E55" s="8"/>
-      <c r="F55" s="8"/>
+      <c r="B55" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C55" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D55" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="E55" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F55" s="8" t="s">
+        <v>69</v>
+      </c>
       <c r="G55" s="8"/>
       <c r="H55" s="8"/>
       <c r="I55" s="8"/>
-      <c r="J55" s="8"/>
+      <c r="J55" s="8" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="56" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B56" s="8"/>
-      <c r="C56" s="8"/>
-      <c r="D56" s="8"/>
-      <c r="E56" s="8"/>
-      <c r="F56" s="8"/>
+      <c r="B56" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C56" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D56" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E56" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F56" s="8" t="s">
+        <v>70</v>
+      </c>
       <c r="G56" s="8"/>
       <c r="H56" s="8"/>
       <c r="I56" s="8"/>
-      <c r="J56" s="8"/>
+      <c r="J56" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="57" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B57" s="8"/>
-      <c r="C57" s="8"/>
-      <c r="D57" s="8"/>
-      <c r="E57" s="8"/>
-      <c r="F57" s="8"/>
+      <c r="B57" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C57" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D57" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E57" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F57" s="8" t="s">
+        <v>71</v>
+      </c>
       <c r="G57" s="8"/>
       <c r="H57" s="8"/>
       <c r="I57" s="8"/>
-      <c r="J57" s="8"/>
+      <c r="J57" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="58" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B58" s="8"/>
-      <c r="C58" s="8"/>
-      <c r="D58" s="8"/>
-      <c r="E58" s="8"/>
-      <c r="F58" s="8"/>
+      <c r="B58" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C58" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D58" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E58" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F58" s="8" t="s">
+        <v>72</v>
+      </c>
       <c r="G58" s="8"/>
       <c r="H58" s="8"/>
       <c r="I58" s="8"/>
-      <c r="J58" s="8"/>
+      <c r="J58" s="8" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="59" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B59" s="8"/>
-      <c r="C59" s="8"/>
-      <c r="D59" s="8"/>
-      <c r="E59" s="8"/>
-      <c r="F59" s="8"/>
+      <c r="B59" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C59" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D59" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E59" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F59" s="8" t="s">
+        <v>73</v>
+      </c>
       <c r="G59" s="8"/>
       <c r="H59" s="8"/>
       <c r="I59" s="8"/>
-      <c r="J59" s="8"/>
+      <c r="J59" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="60" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B60" s="8"/>
-      <c r="C60" s="8"/>
-      <c r="D60" s="8"/>
-      <c r="E60" s="8"/>
-      <c r="F60" s="8"/>
+      <c r="B60" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C60" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D60" s="8" t="n">
+        <v>21</v>
+      </c>
+      <c r="E60" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F60" s="8" t="s">
+        <v>74</v>
+      </c>
       <c r="G60" s="8"/>
       <c r="H60" s="8"/>
       <c r="I60" s="8"/>
-      <c r="J60" s="8"/>
+      <c r="J60" s="8" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="61" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B61" s="8"/>
-      <c r="C61" s="8"/>
-      <c r="D61" s="8"/>
-      <c r="E61" s="8"/>
-      <c r="F61" s="8"/>
+      <c r="B61" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C61" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D61" s="8" t="n">
+        <v>21</v>
+      </c>
+      <c r="E61" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F61" s="8" t="s">
+        <v>75</v>
+      </c>
       <c r="G61" s="8"/>
       <c r="H61" s="8"/>
       <c r="I61" s="8"/>
-      <c r="J61" s="8"/>
+      <c r="J61" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="62" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B62" s="8"/>
-      <c r="C62" s="8"/>
-      <c r="D62" s="8"/>
-      <c r="E62" s="8"/>
-      <c r="F62" s="8"/>
+      <c r="B62" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C62" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D62" s="8" t="n">
+        <v>21</v>
+      </c>
+      <c r="E62" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F62" s="8" t="s">
+        <v>76</v>
+      </c>
       <c r="G62" s="8"/>
       <c r="H62" s="8"/>
       <c r="I62" s="8"/>
-      <c r="J62" s="8"/>
+      <c r="J62" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="63" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B63" s="8"/>
-      <c r="C63" s="8"/>
-      <c r="D63" s="8"/>
-      <c r="E63" s="8"/>
-      <c r="F63" s="8"/>
+      <c r="B63" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C63" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D63" s="8" t="n">
+        <v>21</v>
+      </c>
+      <c r="E63" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F63" s="8" t="s">
+        <v>77</v>
+      </c>
       <c r="G63" s="8"/>
       <c r="H63" s="8"/>
       <c r="I63" s="8"/>
-      <c r="J63" s="8"/>
+      <c r="J63" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="64" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B64" s="8"/>
-      <c r="C64" s="8"/>
-      <c r="D64" s="8"/>
-      <c r="E64" s="8"/>
-      <c r="F64" s="8"/>
+      <c r="B64" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C64" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D64" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="E64" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F64" s="8" t="s">
+        <v>78</v>
+      </c>
       <c r="G64" s="8"/>
       <c r="H64" s="8"/>
       <c r="I64" s="8"/>
-      <c r="J64" s="8"/>
+      <c r="J64" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="65" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B65" s="8"/>
-      <c r="C65" s="8"/>
-      <c r="D65" s="8"/>
-      <c r="E65" s="8"/>
-      <c r="F65" s="8"/>
+      <c r="B65" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C65" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D65" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="E65" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F65" s="8" t="s">
+        <v>79</v>
+      </c>
       <c r="G65" s="8"/>
       <c r="H65" s="8"/>
       <c r="I65" s="8"/>
-      <c r="J65" s="8"/>
+      <c r="J65" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="66" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B66" s="8"/>
-      <c r="C66" s="8"/>
-      <c r="D66" s="8"/>
-      <c r="E66" s="8"/>
-      <c r="F66" s="8"/>
+      <c r="B66" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C66" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D66" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="E66" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F66" s="8" t="s">
+        <v>80</v>
+      </c>
       <c r="G66" s="8"/>
       <c r="H66" s="8"/>
       <c r="I66" s="8"/>
-      <c r="J66" s="8"/>
+      <c r="J66" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="67" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B67" s="8"/>
-      <c r="C67" s="8"/>
-      <c r="D67" s="8"/>
-      <c r="E67" s="8"/>
-      <c r="F67" s="8"/>
+      <c r="B67" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C67" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D67" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="E67" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F67" s="8" t="s">
+        <v>81</v>
+      </c>
       <c r="G67" s="8"/>
       <c r="H67" s="8"/>
       <c r="I67" s="8"/>
-      <c r="J67" s="8"/>
+      <c r="J67" s="8" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="68" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B68" s="8"/>
-      <c r="C68" s="8"/>
-      <c r="D68" s="8"/>
-      <c r="E68" s="8"/>
-      <c r="F68" s="8"/>
+      <c r="B68" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C68" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D68" s="8" t="n">
+        <v>28</v>
+      </c>
+      <c r="E68" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F68" s="8" t="s">
+        <v>82</v>
+      </c>
       <c r="G68" s="8"/>
       <c r="H68" s="8"/>
       <c r="I68" s="8"/>
-      <c r="J68" s="8"/>
+      <c r="J68" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="69" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B69" s="8"/>
-      <c r="C69" s="8"/>
-      <c r="D69" s="8"/>
-      <c r="E69" s="8"/>
-      <c r="F69" s="8"/>
+      <c r="B69" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C69" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D69" s="8" t="n">
+        <v>28</v>
+      </c>
+      <c r="E69" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F69" s="8" t="s">
+        <v>83</v>
+      </c>
       <c r="G69" s="8"/>
       <c r="H69" s="8"/>
       <c r="I69" s="8"/>
-      <c r="J69" s="8"/>
+      <c r="J69" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="70" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B70" s="8"/>
-      <c r="C70" s="8"/>
-      <c r="D70" s="8"/>
-      <c r="E70" s="8"/>
-      <c r="F70" s="8"/>
+      <c r="B70" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C70" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D70" s="8" t="n">
+        <v>28</v>
+      </c>
+      <c r="E70" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F70" s="8" t="s">
+        <v>84</v>
+      </c>
       <c r="G70" s="8"/>
       <c r="H70" s="8"/>
       <c r="I70" s="8"/>
-      <c r="J70" s="8"/>
+      <c r="J70" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="71" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B71" s="8"/>
-      <c r="C71" s="8"/>
-      <c r="D71" s="8"/>
-      <c r="E71" s="8"/>
-      <c r="F71" s="8"/>
+      <c r="B71" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C71" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D71" s="8" t="n">
+        <v>28</v>
+      </c>
+      <c r="E71" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F71" s="8" t="s">
+        <v>85</v>
+      </c>
       <c r="G71" s="8"/>
       <c r="H71" s="8"/>
       <c r="I71" s="8"/>
-      <c r="J71" s="8"/>
+      <c r="J71" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="72" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B72" s="8"/>
-      <c r="C72" s="8"/>
-      <c r="D72" s="8"/>
-      <c r="E72" s="8"/>
-      <c r="F72" s="8"/>
+      <c r="B72" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C72" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D72" s="8" t="n">
+        <v>29</v>
+      </c>
+      <c r="E72" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F72" s="8" t="s">
+        <v>86</v>
+      </c>
       <c r="G72" s="8"/>
       <c r="H72" s="8"/>
       <c r="I72" s="8"/>
-      <c r="J72" s="8"/>
+      <c r="J72" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="73" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B73" s="8"/>
-      <c r="C73" s="8"/>
-      <c r="D73" s="8"/>
-      <c r="E73" s="8"/>
-      <c r="F73" s="8"/>
+      <c r="B73" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C73" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D73" s="8" t="n">
+        <v>29</v>
+      </c>
+      <c r="E73" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F73" s="8" t="s">
+        <v>87</v>
+      </c>
       <c r="G73" s="8"/>
       <c r="H73" s="8"/>
       <c r="I73" s="8"/>
-      <c r="J73" s="8"/>
+      <c r="J73" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="74" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B74" s="8"/>
-      <c r="C74" s="8"/>
-      <c r="D74" s="8"/>
-      <c r="E74" s="8"/>
-      <c r="F74" s="8"/>
+      <c r="B74" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C74" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D74" s="8" t="n">
+        <v>29</v>
+      </c>
+      <c r="E74" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F74" s="8" t="s">
+        <v>88</v>
+      </c>
       <c r="G74" s="8"/>
       <c r="H74" s="8"/>
       <c r="I74" s="8"/>
-      <c r="J74" s="8"/>
+      <c r="J74" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="75" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B75" s="8"/>
-      <c r="C75" s="8"/>
-      <c r="D75" s="8"/>
-      <c r="E75" s="8"/>
-      <c r="F75" s="8"/>
+      <c r="B75" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C75" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D75" s="8" t="n">
+        <v>29</v>
+      </c>
+      <c r="E75" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F75" s="8" t="s">
+        <v>89</v>
+      </c>
       <c r="G75" s="8"/>
       <c r="H75" s="8"/>
       <c r="I75" s="8"/>
-      <c r="J75" s="8"/>
+      <c r="J75" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="76" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B76" s="8"/>
-      <c r="C76" s="8"/>
-      <c r="D76" s="8"/>
-      <c r="E76" s="8"/>
-      <c r="F76" s="8"/>
+      <c r="B76" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C76" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D76" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="E76" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="F76" s="8" t="s">
+        <v>90</v>
+      </c>
       <c r="G76" s="8"/>
       <c r="H76" s="8"/>
       <c r="I76" s="8"/>
-      <c r="J76" s="8"/>
+      <c r="J76" s="8" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="77" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B77" s="8"/>
-      <c r="C77" s="8"/>
-      <c r="D77" s="8"/>
-      <c r="E77" s="8"/>
-      <c r="F77" s="8"/>
+      <c r="B77" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C77" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D77" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="E77" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="F77" s="8" t="s">
+        <v>91</v>
+      </c>
       <c r="G77" s="8"/>
       <c r="H77" s="8"/>
       <c r="I77" s="8"/>
-      <c r="J77" s="8"/>
+      <c r="J77" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="78" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B78" s="8"/>
-      <c r="C78" s="8"/>
-      <c r="D78" s="8"/>
-      <c r="E78" s="8"/>
-      <c r="F78" s="8"/>
+      <c r="B78" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C78" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D78" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="E78" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="F78" s="8" t="s">
+        <v>92</v>
+      </c>
       <c r="G78" s="8"/>
       <c r="H78" s="8"/>
       <c r="I78" s="8"/>
-      <c r="J78" s="8"/>
+      <c r="J78" s="8" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="79" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B79" s="8"/>
-      <c r="C79" s="8"/>
-      <c r="D79" s="8"/>
-      <c r="E79" s="8"/>
-      <c r="F79" s="8"/>
+      <c r="B79" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C79" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D79" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="E79" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="F79" s="8" t="s">
+        <v>93</v>
+      </c>
       <c r="G79" s="8"/>
       <c r="H79" s="8"/>
       <c r="I79" s="8"/>
-      <c r="J79" s="8"/>
+      <c r="J79" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="80" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B80" s="8"/>
-      <c r="C80" s="8"/>
-      <c r="D80" s="8"/>
-      <c r="E80" s="8"/>
-      <c r="F80" s="8"/>
+      <c r="B80" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C80" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D80" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="E80" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="F80" s="8" t="s">
+        <v>94</v>
+      </c>
       <c r="G80" s="8"/>
       <c r="H80" s="8"/>
       <c r="I80" s="8"/>
-      <c r="J80" s="8"/>
+      <c r="J80" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="81" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B81" s="8"/>
-      <c r="C81" s="8"/>
-      <c r="D81" s="8"/>
-      <c r="E81" s="8"/>
-      <c r="F81" s="8"/>
+      <c r="B81" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C81" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D81" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="E81" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="F81" s="8" t="s">
+        <v>95</v>
+      </c>
       <c r="G81" s="8"/>
       <c r="H81" s="8"/>
       <c r="I81" s="8"/>
-      <c r="J81" s="8"/>
+      <c r="J81" s="8" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="82" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B82" s="8"/>
-      <c r="C82" s="8"/>
-      <c r="D82" s="8"/>
-      <c r="E82" s="8"/>
-      <c r="F82" s="8"/>
+      <c r="B82" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C82" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D82" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="E82" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="F82" s="8" t="s">
+        <v>96</v>
+      </c>
       <c r="G82" s="8"/>
       <c r="H82" s="8"/>
       <c r="I82" s="8"/>
-      <c r="J82" s="8"/>
+      <c r="J82" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="83" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B83" s="8"/>
-      <c r="C83" s="8"/>
-      <c r="D83" s="8"/>
-      <c r="E83" s="8"/>
-      <c r="F83" s="8"/>
+      <c r="B83" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C83" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D83" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="E83" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="F83" s="8" t="s">
+        <v>97</v>
+      </c>
       <c r="G83" s="8"/>
       <c r="H83" s="8"/>
       <c r="I83" s="8"/>
-      <c r="J83" s="8"/>
+      <c r="J83" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="84" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B84" s="8"/>
-      <c r="C84" s="8"/>
-      <c r="D84" s="8"/>
-      <c r="E84" s="8"/>
-      <c r="F84" s="8"/>
+      <c r="B84" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C84" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D84" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="E84" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="F84" s="8" t="s">
+        <v>98</v>
+      </c>
       <c r="G84" s="8"/>
       <c r="H84" s="8"/>
       <c r="I84" s="8"/>
-      <c r="J84" s="8"/>
+      <c r="J84" s="8" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="85" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B85" s="8"/>
-      <c r="C85" s="8"/>
-      <c r="D85" s="8"/>
-      <c r="E85" s="8"/>
-      <c r="F85" s="8"/>
+      <c r="B85" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C85" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D85" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="E85" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="F85" s="8" t="s">
+        <v>99</v>
+      </c>
       <c r="G85" s="8"/>
       <c r="H85" s="8"/>
       <c r="I85" s="8"/>
-      <c r="J85" s="8"/>
+      <c r="J85" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="86" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B86" s="8"/>
-      <c r="C86" s="8"/>
-      <c r="D86" s="8"/>
-      <c r="E86" s="8"/>
-      <c r="F86" s="8"/>
+      <c r="B86" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C86" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D86" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="E86" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="F86" s="8" t="s">
+        <v>100</v>
+      </c>
       <c r="G86" s="8"/>
       <c r="H86" s="8"/>
       <c r="I86" s="8"/>
-      <c r="J86" s="8"/>
+      <c r="J86" s="8" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="87" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B87" s="8"/>
-      <c r="C87" s="8"/>
-      <c r="D87" s="8"/>
-      <c r="E87" s="8"/>
-      <c r="F87" s="8"/>
+      <c r="B87" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C87" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D87" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="E87" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="F87" s="8" t="s">
+        <v>101</v>
+      </c>
       <c r="G87" s="8"/>
       <c r="H87" s="8"/>
       <c r="I87" s="8"/>
-      <c r="J87" s="8"/>
+      <c r="J87" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="88" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B88" s="8"/>
-      <c r="C88" s="8"/>
-      <c r="D88" s="8"/>
-      <c r="E88" s="8"/>
-      <c r="F88" s="8"/>
+      <c r="B88" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C88" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D88" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="E88" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="F88" s="8" t="s">
+        <v>102</v>
+      </c>
       <c r="G88" s="8"/>
       <c r="H88" s="8"/>
       <c r="I88" s="8"/>
-      <c r="J88" s="8"/>
+      <c r="J88" s="8" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="89" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B89" s="8"/>
-      <c r="C89" s="8"/>
-      <c r="D89" s="8"/>
-      <c r="E89" s="8"/>
-      <c r="F89" s="8"/>
+      <c r="B89" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C89" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D89" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="E89" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="F89" s="8" t="s">
+        <v>103</v>
+      </c>
       <c r="G89" s="8"/>
       <c r="H89" s="8"/>
       <c r="I89" s="8"/>
-      <c r="J89" s="8"/>
+      <c r="J89" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="90" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B90" s="8"/>
-      <c r="C90" s="8"/>
-      <c r="D90" s="8"/>
-      <c r="E90" s="8"/>
-      <c r="F90" s="8"/>
+      <c r="B90" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C90" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D90" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="E90" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="F90" s="8" t="s">
+        <v>104</v>
+      </c>
       <c r="G90" s="8"/>
       <c r="H90" s="8"/>
       <c r="I90" s="8"/>
-      <c r="J90" s="8"/>
+      <c r="J90" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="91" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B91" s="8"/>
-      <c r="C91" s="8"/>
-      <c r="D91" s="8"/>
-      <c r="E91" s="8"/>
-      <c r="F91" s="8"/>
+      <c r="B91" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C91" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D91" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="E91" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="F91" s="8" t="s">
+        <v>105</v>
+      </c>
       <c r="G91" s="8"/>
       <c r="H91" s="8"/>
       <c r="I91" s="8"/>
-      <c r="J91" s="8"/>
+      <c r="J91" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="92" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B92" s="8"/>
-      <c r="C92" s="8"/>
-      <c r="D92" s="8"/>
-      <c r="E92" s="8"/>
-      <c r="F92" s="8"/>
+      <c r="B92" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C92" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D92" s="8" t="n">
+        <v>18</v>
+      </c>
+      <c r="E92" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="F92" s="8" t="s">
+        <v>106</v>
+      </c>
       <c r="G92" s="8"/>
       <c r="H92" s="8"/>
       <c r="I92" s="8"/>
-      <c r="J92" s="8"/>
+      <c r="J92" s="8" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="93" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B93" s="8"/>
-      <c r="C93" s="8"/>
-      <c r="D93" s="8"/>
-      <c r="E93" s="8"/>
-      <c r="F93" s="8"/>
+      <c r="B93" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C93" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D93" s="8" t="n">
+        <v>18</v>
+      </c>
+      <c r="E93" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="F93" s="8" t="s">
+        <v>107</v>
+      </c>
       <c r="G93" s="8"/>
       <c r="H93" s="8"/>
       <c r="I93" s="8"/>
-      <c r="J93" s="8"/>
+      <c r="J93" s="8" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="94" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B94" s="8"/>
-      <c r="C94" s="8"/>
-      <c r="D94" s="8"/>
-      <c r="E94" s="8"/>
-      <c r="F94" s="8"/>
+      <c r="B94" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C94" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D94" s="8" t="n">
+        <v>18</v>
+      </c>
+      <c r="E94" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="F94" s="8" t="s">
+        <v>108</v>
+      </c>
       <c r="G94" s="8"/>
       <c r="H94" s="8"/>
       <c r="I94" s="8"/>
-      <c r="J94" s="8"/>
+      <c r="J94" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="95" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B95" s="8"/>
-      <c r="C95" s="8"/>
-      <c r="D95" s="8"/>
-      <c r="E95" s="8"/>
-      <c r="F95" s="8"/>
+      <c r="B95" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C95" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D95" s="8" t="n">
+        <v>18</v>
+      </c>
+      <c r="E95" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="F95" s="8" t="s">
+        <v>109</v>
+      </c>
       <c r="G95" s="8"/>
       <c r="H95" s="8"/>
       <c r="I95" s="8"/>
-      <c r="J95" s="8"/>
+      <c r="J95" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="96" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B96" s="8"/>
-      <c r="C96" s="8"/>
-      <c r="D96" s="8"/>
-      <c r="E96" s="8"/>
-      <c r="F96" s="8"/>
+      <c r="B96" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C96" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D96" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="E96" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="F96" s="8" t="s">
+        <v>110</v>
+      </c>
       <c r="G96" s="8"/>
       <c r="H96" s="8"/>
       <c r="I96" s="8"/>
-      <c r="J96" s="8"/>
+      <c r="J96" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="97" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B97" s="8"/>
-      <c r="C97" s="8"/>
-      <c r="D97" s="8"/>
-      <c r="E97" s="8"/>
-      <c r="F97" s="8"/>
+      <c r="B97" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C97" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D97" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="E97" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="F97" s="8" t="s">
+        <v>111</v>
+      </c>
       <c r="G97" s="8"/>
       <c r="H97" s="8"/>
       <c r="I97" s="8"/>
-      <c r="J97" s="8"/>
+      <c r="J97" s="8" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="98" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B98" s="8"/>
-      <c r="C98" s="8"/>
-      <c r="D98" s="8"/>
-      <c r="E98" s="8"/>
-      <c r="F98" s="8"/>
+      <c r="B98" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C98" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D98" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="E98" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="F98" s="8" t="s">
+        <v>112</v>
+      </c>
       <c r="G98" s="8"/>
       <c r="H98" s="8"/>
       <c r="I98" s="8"/>
-      <c r="J98" s="8"/>
+      <c r="J98" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="99" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B99" s="8"/>
-      <c r="C99" s="8"/>
-      <c r="D99" s="8"/>
-      <c r="E99" s="8"/>
-      <c r="F99" s="8"/>
+      <c r="B99" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C99" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D99" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="E99" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="F99" s="8" t="s">
+        <v>113</v>
+      </c>
       <c r="G99" s="8"/>
       <c r="H99" s="8"/>
       <c r="I99" s="8"/>
-      <c r="J99" s="8"/>
+      <c r="J99" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="100" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B100" s="8"/>
-      <c r="C100" s="8"/>
-      <c r="D100" s="8"/>
-      <c r="E100" s="8"/>
-      <c r="F100" s="8"/>
+      <c r="B100" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C100" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D100" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="E100" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="F100" s="8" t="s">
+        <v>114</v>
+      </c>
       <c r="G100" s="8"/>
       <c r="H100" s="8"/>
       <c r="I100" s="8"/>
-      <c r="J100" s="8"/>
+      <c r="J100" s="8" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="101" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B101" s="8"/>
-      <c r="C101" s="8"/>
-      <c r="D101" s="8"/>
-      <c r="E101" s="8"/>
-      <c r="F101" s="8"/>
+      <c r="B101" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C101" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D101" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="E101" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="F101" s="8" t="s">
+        <v>115</v>
+      </c>
       <c r="G101" s="8"/>
       <c r="H101" s="8"/>
       <c r="I101" s="8"/>
-      <c r="J101" s="8"/>
+      <c r="J101" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="102" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B102" s="8"/>
-      <c r="C102" s="8"/>
-      <c r="D102" s="8"/>
-      <c r="E102" s="8"/>
-      <c r="F102" s="8"/>
+      <c r="B102" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C102" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D102" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="E102" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="F102" s="8" t="s">
+        <v>116</v>
+      </c>
       <c r="G102" s="8"/>
       <c r="H102" s="8"/>
       <c r="I102" s="8"/>
-      <c r="J102" s="8"/>
+      <c r="J102" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="103" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B103" s="8"/>
-      <c r="C103" s="8"/>
-      <c r="D103" s="8"/>
-      <c r="E103" s="8"/>
-      <c r="F103" s="8"/>
+      <c r="B103" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C103" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D103" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="E103" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="F103" s="8" t="s">
+        <v>117</v>
+      </c>
       <c r="G103" s="8"/>
       <c r="H103" s="8"/>
       <c r="I103" s="8"/>
-      <c r="J103" s="8"/>
+      <c r="J103" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="104" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B104" s="8"/>
-      <c r="C104" s="8"/>
-      <c r="D104" s="8"/>
-      <c r="E104" s="8"/>
-      <c r="F104" s="8"/>
+      <c r="B104" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C104" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D104" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="E104" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="F104" s="8" t="s">
+        <v>118</v>
+      </c>
       <c r="G104" s="8"/>
       <c r="H104" s="8"/>
       <c r="I104" s="8"/>
-      <c r="J104" s="8"/>
+      <c r="J104" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="105" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B105" s="8"/>
-      <c r="C105" s="8"/>
-      <c r="D105" s="8"/>
-      <c r="E105" s="8"/>
-      <c r="F105" s="8"/>
+      <c r="B105" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C105" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D105" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="E105" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="F105" s="8" t="s">
+        <v>119</v>
+      </c>
       <c r="G105" s="8"/>
       <c r="H105" s="8"/>
       <c r="I105" s="8"/>
-      <c r="J105" s="8"/>
+      <c r="J105" s="8" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="106" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B106" s="8"/>
-      <c r="C106" s="8"/>
-      <c r="D106" s="8"/>
-      <c r="E106" s="8"/>
-      <c r="F106" s="8"/>
+      <c r="B106" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C106" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D106" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="E106" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="F106" s="8" t="s">
+        <v>94</v>
+      </c>
       <c r="G106" s="8"/>
       <c r="H106" s="8"/>
       <c r="I106" s="8"/>
-      <c r="J106" s="8"/>
+      <c r="J106" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="107" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B107" s="8"/>
-      <c r="C107" s="8"/>
-      <c r="D107" s="8"/>
-      <c r="E107" s="8"/>
-      <c r="F107" s="8"/>
+      <c r="B107" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C107" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D107" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="E107" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="F107" s="8" t="s">
+        <v>120</v>
+      </c>
       <c r="G107" s="8"/>
       <c r="H107" s="8"/>
       <c r="I107" s="8"/>
-      <c r="J107" s="8"/>
+      <c r="J107" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="108" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B108" s="8"/>
-      <c r="C108" s="8"/>
-      <c r="D108" s="8"/>
-      <c r="E108" s="8"/>
-      <c r="F108" s="8"/>
+      <c r="B108" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C108" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D108" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E108" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="F108" s="8" t="s">
+        <v>121</v>
+      </c>
       <c r="G108" s="8"/>
       <c r="H108" s="8"/>
       <c r="I108" s="8"/>
-      <c r="J108" s="8"/>
+      <c r="J108" s="8" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="109" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B109" s="8"/>
-      <c r="C109" s="8"/>
-      <c r="D109" s="8"/>
-      <c r="E109" s="8"/>
-      <c r="F109" s="8"/>
+      <c r="B109" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C109" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D109" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E109" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="F109" s="8" t="s">
+        <v>122</v>
+      </c>
       <c r="G109" s="8"/>
       <c r="H109" s="8"/>
       <c r="I109" s="8"/>
-      <c r="J109" s="8"/>
+      <c r="J109" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="110" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B110" s="8"/>
-      <c r="C110" s="8"/>
-      <c r="D110" s="8"/>
-      <c r="E110" s="8"/>
-      <c r="F110" s="8"/>
+      <c r="B110" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C110" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D110" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E110" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="F110" s="8" t="s">
+        <v>123</v>
+      </c>
       <c r="G110" s="8"/>
       <c r="H110" s="8"/>
       <c r="I110" s="8"/>
-      <c r="J110" s="8"/>
+      <c r="J110" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="111" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B111" s="8"/>
-      <c r="C111" s="8"/>
-      <c r="D111" s="8"/>
-      <c r="E111" s="8"/>
-      <c r="F111" s="8"/>
+      <c r="B111" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C111" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D111" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E111" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="F111" s="8" t="s">
+        <v>124</v>
+      </c>
       <c r="G111" s="8"/>
       <c r="H111" s="8"/>
       <c r="I111" s="8"/>
-      <c r="J111" s="8"/>
+      <c r="J111" s="8" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="112" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B112" s="8"/>
-      <c r="C112" s="8"/>
-      <c r="D112" s="8"/>
-      <c r="E112" s="8"/>
-      <c r="F112" s="8"/>
+      <c r="B112" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C112" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D112" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E112" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="F112" s="8" t="s">
+        <v>125</v>
+      </c>
       <c r="G112" s="8"/>
       <c r="H112" s="8"/>
       <c r="I112" s="8"/>
-      <c r="J112" s="8"/>
+      <c r="J112" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="113" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B113" s="8"/>
-      <c r="C113" s="8"/>
-      <c r="D113" s="8"/>
-      <c r="E113" s="8"/>
-      <c r="F113" s="8"/>
+      <c r="B113" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C113" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D113" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E113" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="F113" s="8" t="s">
+        <v>126</v>
+      </c>
       <c r="G113" s="8"/>
       <c r="H113" s="8"/>
       <c r="I113" s="8"/>
-      <c r="J113" s="8"/>
+      <c r="J113" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="114" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B114" s="8"/>
-      <c r="C114" s="8"/>
-      <c r="D114" s="8"/>
-      <c r="E114" s="8"/>
-      <c r="F114" s="8"/>
+      <c r="B114" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C114" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D114" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E114" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="F114" s="8" t="s">
+        <v>64</v>
+      </c>
       <c r="G114" s="8"/>
       <c r="H114" s="8"/>
       <c r="I114" s="8"/>
-      <c r="J114" s="8"/>
+      <c r="J114" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="115" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B115" s="8"/>
-      <c r="C115" s="8"/>
-      <c r="D115" s="8"/>
-      <c r="E115" s="8"/>
-      <c r="F115" s="8"/>
+      <c r="B115" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C115" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D115" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E115" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="F115" s="8" t="s">
+        <v>127</v>
+      </c>
       <c r="G115" s="8"/>
       <c r="H115" s="8"/>
       <c r="I115" s="8"/>
-      <c r="J115" s="8"/>
+      <c r="J115" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="116" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B116" s="8"/>
-      <c r="C116" s="8"/>
-      <c r="D116" s="8"/>
-      <c r="E116" s="8"/>
-      <c r="F116" s="8"/>
+      <c r="B116" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C116" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D116" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="E116" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="F116" s="8" t="s">
+        <v>128</v>
+      </c>
       <c r="G116" s="8"/>
       <c r="H116" s="8"/>
       <c r="I116" s="8"/>
-      <c r="J116" s="8"/>
+      <c r="J116" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="117" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B117" s="8"/>
-      <c r="C117" s="8"/>
-      <c r="D117" s="8"/>
-      <c r="E117" s="8"/>
-      <c r="F117" s="8"/>
+      <c r="B117" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C117" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D117" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="E117" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="F117" s="8" t="s">
+        <v>129</v>
+      </c>
       <c r="G117" s="8"/>
       <c r="H117" s="8"/>
       <c r="I117" s="8"/>
-      <c r="J117" s="8"/>
+      <c r="J117" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="118" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B118" s="8"/>
-      <c r="C118" s="8"/>
-      <c r="D118" s="8"/>
-      <c r="E118" s="8"/>
-      <c r="F118" s="8"/>
+      <c r="B118" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C118" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D118" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="E118" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="F118" s="8" t="s">
+        <v>130</v>
+      </c>
       <c r="G118" s="8"/>
       <c r="H118" s="8"/>
       <c r="I118" s="8"/>
-      <c r="J118" s="8"/>
+      <c r="J118" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="119" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B119" s="8"/>
-      <c r="C119" s="8"/>
-      <c r="D119" s="8"/>
-      <c r="E119" s="8"/>
-      <c r="F119" s="8"/>
+      <c r="B119" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C119" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D119" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="E119" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="F119" s="8" t="s">
+        <v>131</v>
+      </c>
       <c r="G119" s="8"/>
       <c r="H119" s="8"/>
       <c r="I119" s="8"/>
-      <c r="J119" s="8"/>
+      <c r="J119" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="120" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B120" s="8"/>
-      <c r="C120" s="8"/>
-      <c r="D120" s="8"/>
-      <c r="E120" s="8"/>
-      <c r="F120" s="8"/>
+      <c r="B120" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C120" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D120" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="E120" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="F120" s="8" t="s">
+        <v>132</v>
+      </c>
       <c r="G120" s="8"/>
       <c r="H120" s="8"/>
       <c r="I120" s="8"/>
-      <c r="J120" s="8"/>
+      <c r="J120" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="121" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B121" s="8"/>
-      <c r="C121" s="8"/>
-      <c r="D121" s="8"/>
-      <c r="E121" s="8"/>
-      <c r="F121" s="8"/>
+      <c r="B121" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C121" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D121" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="E121" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="F121" s="8" t="s">
+        <v>133</v>
+      </c>
       <c r="G121" s="8"/>
       <c r="H121" s="8"/>
       <c r="I121" s="8"/>
-      <c r="J121" s="8"/>
+      <c r="J121" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="122" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B122" s="8"/>
-      <c r="C122" s="8"/>
-      <c r="D122" s="8"/>
-      <c r="E122" s="8"/>
-      <c r="F122" s="8"/>
+      <c r="B122" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C122" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D122" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="E122" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="F122" s="8" t="s">
+        <v>134</v>
+      </c>
       <c r="G122" s="8"/>
       <c r="H122" s="8"/>
       <c r="I122" s="8"/>
-      <c r="J122" s="8"/>
+      <c r="J122" s="8" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="123" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B123" s="8"/>
-      <c r="C123" s="8"/>
-      <c r="D123" s="8"/>
-      <c r="E123" s="8"/>
-      <c r="F123" s="8"/>
+      <c r="B123" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C123" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D123" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="E123" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="F123" s="8" t="s">
+        <v>135</v>
+      </c>
       <c r="G123" s="8"/>
       <c r="H123" s="8"/>
       <c r="I123" s="8"/>
-      <c r="J123" s="8"/>
+      <c r="J123" s="8" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="124" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B124" s="8"/>
-      <c r="C124" s="8"/>
-      <c r="D124" s="8"/>
-      <c r="E124" s="8"/>
-      <c r="F124" s="8"/>
+      <c r="B124" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C124" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D124" s="8" t="n">
+        <v>16</v>
+      </c>
+      <c r="E124" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="F124" s="8" t="s">
+        <v>136</v>
+      </c>
       <c r="G124" s="8"/>
       <c r="H124" s="8"/>
       <c r="I124" s="8"/>
-      <c r="J124" s="8"/>
+      <c r="J124" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="125" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B125" s="8"/>
-      <c r="C125" s="8"/>
-      <c r="D125" s="8"/>
-      <c r="E125" s="8"/>
-      <c r="F125" s="8"/>
+      <c r="B125" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C125" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D125" s="8" t="n">
+        <v>16</v>
+      </c>
+      <c r="E125" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="F125" s="8" t="s">
+        <v>137</v>
+      </c>
       <c r="G125" s="8"/>
       <c r="H125" s="8"/>
       <c r="I125" s="8"/>
-      <c r="J125" s="8"/>
+      <c r="J125" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="126" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B126" s="8"/>
-      <c r="C126" s="8"/>
-      <c r="D126" s="8"/>
-      <c r="E126" s="8"/>
-      <c r="F126" s="8"/>
+      <c r="B126" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C126" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D126" s="8" t="n">
+        <v>16</v>
+      </c>
+      <c r="E126" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="F126" s="8" t="s">
+        <v>138</v>
+      </c>
       <c r="G126" s="8"/>
       <c r="H126" s="8"/>
       <c r="I126" s="8"/>
-      <c r="J126" s="8"/>
+      <c r="J126" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="127" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B127" s="8"/>
-      <c r="C127" s="8"/>
-      <c r="D127" s="8"/>
-      <c r="E127" s="8"/>
-      <c r="F127" s="8"/>
+      <c r="B127" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C127" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D127" s="8" t="n">
+        <v>16</v>
+      </c>
+      <c r="E127" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="F127" s="8" t="s">
+        <v>45</v>
+      </c>
       <c r="G127" s="8"/>
       <c r="H127" s="8"/>
       <c r="I127" s="8"/>
-      <c r="J127" s="8"/>
+      <c r="J127" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="128" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B128" s="8"/>
-      <c r="C128" s="8"/>
-      <c r="D128" s="8"/>
-      <c r="E128" s="8"/>
-      <c r="F128" s="8"/>
+      <c r="B128" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C128" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D128" s="8" t="n">
+        <v>17</v>
+      </c>
+      <c r="E128" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="F128" s="8" t="s">
+        <v>139</v>
+      </c>
       <c r="G128" s="8"/>
       <c r="H128" s="8"/>
       <c r="I128" s="8"/>
-      <c r="J128" s="8"/>
+      <c r="J128" s="8" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="129" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B129" s="8"/>
-      <c r="C129" s="8"/>
-      <c r="D129" s="8"/>
-      <c r="E129" s="8"/>
-      <c r="F129" s="8"/>
+      <c r="B129" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C129" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D129" s="8" t="n">
+        <v>17</v>
+      </c>
+      <c r="E129" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="F129" s="8" t="s">
+        <v>140</v>
+      </c>
       <c r="G129" s="8"/>
       <c r="H129" s="8"/>
       <c r="I129" s="8"/>
-      <c r="J129" s="8"/>
+      <c r="J129" s="8" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="130" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B130" s="8"/>
-      <c r="C130" s="8"/>
-      <c r="D130" s="8"/>
-      <c r="E130" s="8"/>
-      <c r="F130" s="8"/>
+      <c r="B130" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C130" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D130" s="8" t="n">
+        <v>17</v>
+      </c>
+      <c r="E130" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="F130" s="8" t="s">
+        <v>141</v>
+      </c>
       <c r="G130" s="8"/>
       <c r="H130" s="8"/>
       <c r="I130" s="8"/>
-      <c r="J130" s="8"/>
+      <c r="J130" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="131" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B131" s="8"/>
-      <c r="C131" s="8"/>
-      <c r="D131" s="8"/>
-      <c r="E131" s="8"/>
-      <c r="F131" s="8"/>
+      <c r="B131" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C131" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D131" s="8" t="n">
+        <v>17</v>
+      </c>
+      <c r="E131" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="F131" s="8" t="s">
+        <v>142</v>
+      </c>
       <c r="G131" s="8"/>
       <c r="H131" s="8"/>
       <c r="I131" s="8"/>
-      <c r="J131" s="8"/>
+      <c r="J131" s="8" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="132" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B132" s="8"/>
-      <c r="C132" s="8"/>
-      <c r="D132" s="8"/>
-      <c r="E132" s="8"/>
-      <c r="F132" s="8"/>
+      <c r="B132" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C132" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D132" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="E132" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="F132" s="8" t="s">
+        <v>143</v>
+      </c>
       <c r="G132" s="8"/>
       <c r="H132" s="8"/>
       <c r="I132" s="8"/>
-      <c r="J132" s="8"/>
+      <c r="J132" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="133" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B133" s="8"/>
-      <c r="C133" s="8"/>
-      <c r="D133" s="8"/>
-      <c r="E133" s="8"/>
-      <c r="F133" s="8"/>
+      <c r="B133" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C133" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D133" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="E133" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="F133" s="8" t="s">
+        <v>144</v>
+      </c>
       <c r="G133" s="8"/>
       <c r="H133" s="8"/>
       <c r="I133" s="8"/>
-      <c r="J133" s="8"/>
+      <c r="J133" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="134" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B134" s="8"/>
-      <c r="C134" s="8"/>
-      <c r="D134" s="8"/>
-      <c r="E134" s="8"/>
-      <c r="F134" s="8"/>
+      <c r="B134" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C134" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D134" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="E134" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="F134" s="8" t="s">
+        <v>145</v>
+      </c>
       <c r="G134" s="8"/>
       <c r="H134" s="8"/>
       <c r="I134" s="8"/>
-      <c r="J134" s="8"/>
+      <c r="J134" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="135" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B135" s="8"/>
-      <c r="C135" s="8"/>
-      <c r="D135" s="8"/>
-      <c r="E135" s="8"/>
-      <c r="F135" s="8"/>
+      <c r="B135" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C135" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D135" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="E135" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="F135" s="8" t="s">
+        <v>146</v>
+      </c>
       <c r="G135" s="8"/>
       <c r="H135" s="8"/>
       <c r="I135" s="8"/>
-      <c r="J135" s="8"/>
+      <c r="J135" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="136" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B136" s="8"/>
-      <c r="C136" s="8"/>
-      <c r="D136" s="8"/>
-      <c r="E136" s="8"/>
-      <c r="F136" s="8"/>
+      <c r="B136" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C136" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D136" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="E136" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="F136" s="8" t="s">
+        <v>147</v>
+      </c>
       <c r="G136" s="8"/>
       <c r="H136" s="8"/>
       <c r="I136" s="8"/>
-      <c r="J136" s="8"/>
+      <c r="J136" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="137" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B137" s="8"/>
-      <c r="C137" s="8"/>
-      <c r="D137" s="8"/>
-      <c r="E137" s="8"/>
-      <c r="F137" s="8"/>
+      <c r="B137" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C137" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D137" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="E137" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="F137" s="8" t="s">
+        <v>148</v>
+      </c>
       <c r="G137" s="8"/>
       <c r="H137" s="8"/>
       <c r="I137" s="8"/>
-      <c r="J137" s="8"/>
+      <c r="J137" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="138" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B138" s="8"/>
-      <c r="C138" s="8"/>
-      <c r="D138" s="8"/>
-      <c r="E138" s="8"/>
-      <c r="F138" s="8"/>
+      <c r="B138" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C138" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D138" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="E138" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="F138" s="8" t="s">
+        <v>149</v>
+      </c>
       <c r="G138" s="8"/>
       <c r="H138" s="8"/>
       <c r="I138" s="8"/>
-      <c r="J138" s="8"/>
+      <c r="J138" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="139" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B139" s="8"/>
-      <c r="C139" s="8"/>
-      <c r="D139" s="8"/>
-      <c r="E139" s="8"/>
-      <c r="F139" s="8"/>
+      <c r="B139" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C139" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D139" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="E139" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="F139" s="8" t="s">
+        <v>150</v>
+      </c>
       <c r="G139" s="8"/>
       <c r="H139" s="8"/>
       <c r="I139" s="8"/>
-      <c r="J139" s="8"/>
+      <c r="J139" s="8" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="140" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B140" s="8"/>
-      <c r="C140" s="8"/>
-      <c r="D140" s="8"/>
-      <c r="E140" s="8"/>
-      <c r="F140" s="8"/>
+      <c r="B140" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C140" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D140" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="E140" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="F140" s="8" t="s">
+        <v>151</v>
+      </c>
       <c r="G140" s="8"/>
       <c r="H140" s="8"/>
       <c r="I140" s="8"/>
-      <c r="J140" s="8"/>
+      <c r="J140" s="8" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="141" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B141" s="8"/>
-      <c r="C141" s="8"/>
-      <c r="D141" s="8"/>
-      <c r="E141" s="8"/>
-      <c r="F141" s="8"/>
+      <c r="B141" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C141" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D141" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="E141" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="F141" s="8" t="s">
+        <v>152</v>
+      </c>
       <c r="G141" s="8"/>
       <c r="H141" s="8"/>
       <c r="I141" s="8"/>
-      <c r="J141" s="8"/>
+      <c r="J141" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="142" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B142" s="8"/>
-      <c r="C142" s="8"/>
-      <c r="D142" s="8"/>
-      <c r="E142" s="8"/>
-      <c r="F142" s="8"/>
+      <c r="B142" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C142" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D142" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="E142" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="F142" s="8" t="s">
+        <v>153</v>
+      </c>
       <c r="G142" s="8"/>
       <c r="H142" s="8"/>
       <c r="I142" s="8"/>
-      <c r="J142" s="8"/>
+      <c r="J142" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="143" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B143" s="8"/>
-      <c r="C143" s="8"/>
-      <c r="D143" s="8"/>
-      <c r="E143" s="8"/>
-      <c r="F143" s="8"/>
+      <c r="B143" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C143" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D143" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="E143" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="F143" s="8" t="s">
+        <v>154</v>
+      </c>
       <c r="G143" s="8"/>
       <c r="H143" s="8"/>
       <c r="I143" s="8"/>
-      <c r="J143" s="8"/>
+      <c r="J143" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="144" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B144" s="8"/>
-      <c r="C144" s="8"/>
-      <c r="D144" s="8"/>
-      <c r="E144" s="8"/>
-      <c r="F144" s="8"/>
+      <c r="B144" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C144" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D144" s="8" t="n">
+        <v>31</v>
+      </c>
+      <c r="E144" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="F144" s="8" t="s">
+        <v>155</v>
+      </c>
       <c r="G144" s="8"/>
       <c r="H144" s="8"/>
       <c r="I144" s="8"/>
-      <c r="J144" s="8"/>
+      <c r="J144" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="145" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B145" s="8"/>
-      <c r="C145" s="8"/>
-      <c r="D145" s="8"/>
-      <c r="E145" s="8"/>
-      <c r="F145" s="8"/>
+      <c r="B145" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C145" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D145" s="8" t="n">
+        <v>31</v>
+      </c>
+      <c r="E145" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="F145" s="8" t="s">
+        <v>156</v>
+      </c>
       <c r="G145" s="8"/>
       <c r="H145" s="8"/>
       <c r="I145" s="8"/>
-      <c r="J145" s="8"/>
+      <c r="J145" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="146" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B146" s="8"/>
-      <c r="C146" s="8"/>
-      <c r="D146" s="8"/>
-      <c r="E146" s="8"/>
-      <c r="F146" s="8"/>
+      <c r="B146" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C146" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D146" s="8" t="n">
+        <v>31</v>
+      </c>
+      <c r="E146" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="F146" s="8" t="s">
+        <v>157</v>
+      </c>
       <c r="G146" s="8"/>
       <c r="H146" s="8"/>
       <c r="I146" s="8"/>
-      <c r="J146" s="8"/>
+      <c r="J146" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="147" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B147" s="8"/>
-      <c r="C147" s="8"/>
-      <c r="D147" s="8"/>
-      <c r="E147" s="8"/>
-      <c r="F147" s="8"/>
+      <c r="B147" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C147" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D147" s="8" t="n">
+        <v>31</v>
+      </c>
+      <c r="E147" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="F147" s="8" t="s">
+        <v>105</v>
+      </c>
       <c r="G147" s="8"/>
       <c r="H147" s="8"/>
       <c r="I147" s="8"/>
-      <c r="J147" s="8"/>
+      <c r="J147" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="148" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B148" s="8"/>
-      <c r="C148" s="8"/>
-      <c r="D148" s="8"/>
-      <c r="E148" s="8"/>
-      <c r="F148" s="8"/>
+      <c r="B148" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C148" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D148" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="E148" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="F148" s="8" t="s">
+        <v>158</v>
+      </c>
       <c r="G148" s="8"/>
       <c r="H148" s="8"/>
       <c r="I148" s="8"/>
-      <c r="J148" s="8"/>
+      <c r="J148" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="149" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B149" s="8"/>
-      <c r="C149" s="8"/>
-      <c r="D149" s="8"/>
-      <c r="E149" s="8"/>
-      <c r="F149" s="8"/>
+      <c r="B149" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C149" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D149" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="E149" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="F149" s="8" t="s">
+        <v>159</v>
+      </c>
       <c r="G149" s="8"/>
       <c r="H149" s="8"/>
       <c r="I149" s="8"/>
-      <c r="J149" s="8"/>
+      <c r="J149" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="150" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B150" s="8"/>
-      <c r="C150" s="8"/>
-      <c r="D150" s="8"/>
-      <c r="E150" s="8"/>
-      <c r="F150" s="8"/>
+      <c r="B150" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C150" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D150" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="E150" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="F150" s="8" t="s">
+        <v>160</v>
+      </c>
       <c r="G150" s="8"/>
       <c r="H150" s="8"/>
       <c r="I150" s="8"/>
-      <c r="J150" s="8"/>
+      <c r="J150" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="151" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B151" s="8"/>
-      <c r="C151" s="8"/>
-      <c r="D151" s="8"/>
-      <c r="E151" s="8"/>
-      <c r="F151" s="8"/>
+      <c r="B151" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C151" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D151" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="E151" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="F151" s="8" t="s">
+        <v>161</v>
+      </c>
       <c r="G151" s="8"/>
       <c r="H151" s="8"/>
       <c r="I151" s="8"/>
-      <c r="J151" s="8"/>
+      <c r="J151" s="8" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="152" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B152" s="8"/>
-      <c r="C152" s="8"/>
-      <c r="D152" s="8"/>
-      <c r="E152" s="8"/>
-      <c r="F152" s="8"/>
+      <c r="B152" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C152" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D152" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="E152" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="F152" s="8" t="s">
+        <v>162</v>
+      </c>
       <c r="G152" s="8"/>
       <c r="H152" s="8"/>
       <c r="I152" s="8"/>
-      <c r="J152" s="8"/>
+      <c r="J152" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="153" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B153" s="8"/>
-      <c r="C153" s="8"/>
-      <c r="D153" s="8"/>
-      <c r="E153" s="8"/>
-      <c r="F153" s="8"/>
+      <c r="B153" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C153" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D153" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="E153" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="F153" s="8" t="s">
+        <v>163</v>
+      </c>
       <c r="G153" s="8"/>
       <c r="H153" s="8"/>
       <c r="I153" s="8"/>
-      <c r="J153" s="8"/>
+      <c r="J153" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="154" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B154" s="8"/>
-      <c r="C154" s="8"/>
-      <c r="D154" s="8"/>
-      <c r="E154" s="8"/>
-      <c r="F154" s="8"/>
+      <c r="B154" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C154" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D154" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="E154" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="F154" s="8" t="s">
+        <v>164</v>
+      </c>
       <c r="G154" s="8"/>
       <c r="H154" s="8"/>
       <c r="I154" s="8"/>
-      <c r="J154" s="8"/>
+      <c r="J154" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="155" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B155" s="8"/>
-      <c r="C155" s="8"/>
-      <c r="D155" s="8"/>
-      <c r="E155" s="8"/>
-      <c r="F155" s="8"/>
+      <c r="B155" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C155" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D155" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="E155" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="F155" s="8" t="s">
+        <v>165</v>
+      </c>
       <c r="G155" s="8"/>
       <c r="H155" s="8"/>
       <c r="I155" s="8"/>
-      <c r="J155" s="8"/>
+      <c r="J155" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="156" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B156" s="8"/>
-      <c r="C156" s="8"/>
-      <c r="D156" s="8"/>
-      <c r="E156" s="8"/>
-      <c r="F156" s="8"/>
+      <c r="B156" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C156" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D156" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="E156" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="F156" s="8" t="s">
+        <v>166</v>
+      </c>
       <c r="G156" s="8"/>
       <c r="H156" s="8"/>
       <c r="I156" s="8"/>
-      <c r="J156" s="8"/>
+      <c r="J156" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="157" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B157" s="8"/>
-      <c r="C157" s="8"/>
-      <c r="D157" s="8"/>
-      <c r="E157" s="8"/>
-      <c r="F157" s="8"/>
+      <c r="B157" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C157" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D157" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="E157" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="F157" s="8" t="s">
+        <v>167</v>
+      </c>
       <c r="G157" s="8"/>
       <c r="H157" s="8"/>
       <c r="I157" s="8"/>
-      <c r="J157" s="8"/>
+      <c r="J157" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="158" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B158" s="8"/>
-      <c r="C158" s="8"/>
-      <c r="D158" s="8"/>
-      <c r="E158" s="8"/>
-      <c r="F158" s="8"/>
+      <c r="B158" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C158" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D158" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="E158" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="F158" s="8" t="s">
+        <v>168</v>
+      </c>
       <c r="G158" s="8"/>
       <c r="H158" s="8"/>
       <c r="I158" s="8"/>
-      <c r="J158" s="8"/>
+      <c r="J158" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="159" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B159" s="8"/>
-      <c r="C159" s="8"/>
-      <c r="D159" s="8"/>
-      <c r="E159" s="8"/>
-      <c r="F159" s="8"/>
+      <c r="B159" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C159" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D159" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="E159" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="F159" s="8" t="s">
+        <v>169</v>
+      </c>
       <c r="G159" s="8"/>
       <c r="H159" s="8"/>
       <c r="I159" s="8"/>
-      <c r="J159" s="8"/>
+      <c r="J159" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="160" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B160" s="8"/>
-      <c r="C160" s="8"/>
-      <c r="D160" s="8"/>
-      <c r="E160" s="8"/>
-      <c r="F160" s="8"/>
+      <c r="B160" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C160" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D160" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="E160" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="F160" s="8" t="s">
+        <v>170</v>
+      </c>
       <c r="G160" s="8"/>
       <c r="H160" s="8"/>
       <c r="I160" s="8"/>
-      <c r="J160" s="8"/>
+      <c r="J160" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="161" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B161" s="8"/>
-      <c r="C161" s="8"/>
-      <c r="D161" s="8"/>
-      <c r="E161" s="8"/>
-      <c r="F161" s="8"/>
+      <c r="B161" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C161" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D161" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="E161" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="F161" s="8" t="s">
+        <v>171</v>
+      </c>
       <c r="G161" s="8"/>
       <c r="H161" s="8"/>
       <c r="I161" s="8"/>
-      <c r="J161" s="8"/>
+      <c r="J161" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="162" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B162" s="8"/>
-      <c r="C162" s="8"/>
-      <c r="D162" s="8"/>
-      <c r="E162" s="8"/>
-      <c r="F162" s="8"/>
+      <c r="B162" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C162" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D162" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="E162" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="F162" s="8" t="s">
+        <v>172</v>
+      </c>
       <c r="G162" s="8"/>
       <c r="H162" s="8"/>
       <c r="I162" s="8"/>
-      <c r="J162" s="8"/>
+      <c r="J162" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="163" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B163" s="8"/>
-      <c r="C163" s="8"/>
-      <c r="D163" s="8"/>
-      <c r="E163" s="8"/>
-      <c r="F163" s="8"/>
+      <c r="B163" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C163" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D163" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="E163" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="F163" s="8" t="s">
+        <v>97</v>
+      </c>
       <c r="G163" s="8"/>
       <c r="H163" s="8"/>
       <c r="I163" s="8"/>
-      <c r="J163" s="8"/>
+      <c r="J163" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="164" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B164" s="8"/>
-      <c r="C164" s="8"/>
-      <c r="D164" s="8"/>
-      <c r="E164" s="8"/>
-      <c r="F164" s="8"/>
+      <c r="B164" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C164" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D164" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="E164" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="F164" s="8" t="s">
+        <v>173</v>
+      </c>
       <c r="G164" s="8"/>
       <c r="H164" s="8"/>
       <c r="I164" s="8"/>
-      <c r="J164" s="8"/>
+      <c r="J164" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="165" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B165" s="8"/>
-      <c r="C165" s="8"/>
-      <c r="D165" s="8"/>
-      <c r="E165" s="8"/>
-      <c r="F165" s="8"/>
+      <c r="B165" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C165" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D165" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="E165" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="F165" s="8" t="s">
+        <v>174</v>
+      </c>
       <c r="G165" s="8"/>
       <c r="H165" s="8"/>
       <c r="I165" s="8"/>
-      <c r="J165" s="8"/>
+      <c r="J165" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="166" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B166" s="8"/>
-      <c r="C166" s="8"/>
-      <c r="D166" s="8"/>
-      <c r="E166" s="8"/>
-      <c r="F166" s="8"/>
+      <c r="B166" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C166" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D166" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="E166" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="F166" s="8" t="s">
+        <v>175</v>
+      </c>
       <c r="G166" s="8"/>
       <c r="H166" s="8"/>
       <c r="I166" s="8"/>
-      <c r="J166" s="8"/>
+      <c r="J166" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="167" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B167" s="8"/>
-      <c r="C167" s="8"/>
-      <c r="D167" s="8"/>
-      <c r="E167" s="8"/>
-      <c r="F167" s="8"/>
+      <c r="B167" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C167" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D167" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="E167" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="F167" s="8" t="s">
+        <v>176</v>
+      </c>
       <c r="G167" s="8"/>
       <c r="H167" s="8"/>
       <c r="I167" s="8"/>
-      <c r="J167" s="8"/>
+      <c r="J167" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="168" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B168" s="8"/>
-      <c r="C168" s="8"/>
-      <c r="D168" s="8"/>
-      <c r="E168" s="8"/>
-      <c r="F168" s="8"/>
+      <c r="B168" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C168" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D168" s="8" t="n">
+        <v>21</v>
+      </c>
+      <c r="E168" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="F168" s="8" t="s">
+        <v>177</v>
+      </c>
       <c r="G168" s="8"/>
       <c r="H168" s="8"/>
       <c r="I168" s="8"/>
-      <c r="J168" s="8"/>
+      <c r="J168" s="8" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="169" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B169" s="8"/>
-      <c r="C169" s="8"/>
-      <c r="D169" s="8"/>
-      <c r="E169" s="8"/>
-      <c r="F169" s="8"/>
+      <c r="B169" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C169" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D169" s="8" t="n">
+        <v>21</v>
+      </c>
+      <c r="E169" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="F169" s="8" t="s">
+        <v>178</v>
+      </c>
       <c r="G169" s="8"/>
       <c r="H169" s="8"/>
       <c r="I169" s="8"/>
-      <c r="J169" s="8"/>
+      <c r="J169" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="170" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B170" s="8"/>
-      <c r="C170" s="8"/>
-      <c r="D170" s="8"/>
-      <c r="E170" s="8"/>
-      <c r="F170" s="8"/>
+      <c r="B170" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C170" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D170" s="8" t="n">
+        <v>21</v>
+      </c>
+      <c r="E170" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="F170" s="8" t="s">
+        <v>179</v>
+      </c>
       <c r="G170" s="8"/>
       <c r="H170" s="8"/>
       <c r="I170" s="8"/>
-      <c r="J170" s="8"/>
+      <c r="J170" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="171" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B171" s="8"/>
-      <c r="C171" s="8"/>
-      <c r="D171" s="8"/>
-      <c r="E171" s="8"/>
-      <c r="F171" s="8"/>
+      <c r="B171" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C171" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D171" s="8" t="n">
+        <v>21</v>
+      </c>
+      <c r="E171" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="F171" s="8" t="s">
+        <v>85</v>
+      </c>
       <c r="G171" s="8"/>
       <c r="H171" s="8"/>
       <c r="I171" s="8"/>
-      <c r="J171" s="8"/>
+      <c r="J171" s="8" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="172" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B172" s="8"/>
-      <c r="C172" s="8"/>
-      <c r="D172" s="8"/>
-      <c r="E172" s="8"/>
-      <c r="F172" s="8"/>
+      <c r="B172" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C172" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D172" s="8" t="n">
+        <v>27</v>
+      </c>
+      <c r="E172" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="F172" s="8" t="s">
+        <v>180</v>
+      </c>
       <c r="G172" s="8"/>
       <c r="H172" s="8"/>
       <c r="I172" s="8"/>
-      <c r="J172" s="8"/>
+      <c r="J172" s="8" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="173" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B173" s="8"/>
-      <c r="C173" s="8"/>
-      <c r="D173" s="8"/>
-      <c r="E173" s="8"/>
-      <c r="F173" s="8"/>
+      <c r="B173" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C173" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D173" s="8" t="n">
+        <v>27</v>
+      </c>
+      <c r="E173" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="F173" s="8" t="s">
+        <v>181</v>
+      </c>
       <c r="G173" s="8"/>
       <c r="H173" s="8"/>
       <c r="I173" s="8"/>
-      <c r="J173" s="8"/>
+      <c r="J173" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="174" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B174" s="8"/>
-      <c r="C174" s="8"/>
-      <c r="D174" s="8"/>
-      <c r="E174" s="8"/>
-      <c r="F174" s="8"/>
+      <c r="B174" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C174" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D174" s="8" t="n">
+        <v>27</v>
+      </c>
+      <c r="E174" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="F174" s="8" t="s">
+        <v>182</v>
+      </c>
       <c r="G174" s="8"/>
       <c r="H174" s="8"/>
       <c r="I174" s="8"/>
-      <c r="J174" s="8"/>
+      <c r="J174" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="175" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B175" s="8"/>
-      <c r="C175" s="8"/>
-      <c r="D175" s="8"/>
-      <c r="E175" s="8"/>
-      <c r="F175" s="8"/>
+      <c r="B175" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C175" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D175" s="8" t="n">
+        <v>27</v>
+      </c>
+      <c r="E175" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="F175" s="8" t="s">
+        <v>183</v>
+      </c>
       <c r="G175" s="8"/>
       <c r="H175" s="8"/>
       <c r="I175" s="8"/>
-      <c r="J175" s="8"/>
+      <c r="J175" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="176" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B176" s="8"/>
-      <c r="C176" s="8"/>
-      <c r="D176" s="8"/>
-      <c r="E176" s="8"/>
-      <c r="F176" s="8"/>
+      <c r="B176" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C176" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D176" s="8" t="n">
+        <v>28</v>
+      </c>
+      <c r="E176" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="F176" s="8" t="s">
+        <v>184</v>
+      </c>
       <c r="G176" s="8"/>
       <c r="H176" s="8"/>
       <c r="I176" s="8"/>
-      <c r="J176" s="8"/>
+      <c r="J176" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="177" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B177" s="8"/>
-      <c r="C177" s="8"/>
-      <c r="D177" s="8"/>
-      <c r="E177" s="8"/>
-      <c r="F177" s="8"/>
+      <c r="B177" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C177" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D177" s="8" t="n">
+        <v>28</v>
+      </c>
+      <c r="E177" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="F177" s="8" t="s">
+        <v>185</v>
+      </c>
       <c r="G177" s="8"/>
       <c r="H177" s="8"/>
       <c r="I177" s="8"/>
-      <c r="J177" s="8"/>
+      <c r="J177" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="178" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B178" s="8"/>
-      <c r="C178" s="8"/>
-      <c r="D178" s="8"/>
-      <c r="E178" s="8"/>
-      <c r="F178" s="8"/>
+      <c r="B178" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C178" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D178" s="8" t="n">
+        <v>28</v>
+      </c>
+      <c r="E178" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="F178" s="8" t="s">
+        <v>186</v>
+      </c>
       <c r="G178" s="8"/>
       <c r="H178" s="8"/>
       <c r="I178" s="8"/>
-      <c r="J178" s="8"/>
+      <c r="J178" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="179" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B179" s="8"/>
-      <c r="C179" s="8"/>
-      <c r="D179" s="8"/>
-      <c r="E179" s="8"/>
-      <c r="F179" s="8"/>
+      <c r="B179" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C179" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D179" s="8" t="n">
+        <v>28</v>
+      </c>
+      <c r="E179" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="F179" s="8" t="s">
+        <v>187</v>
+      </c>
       <c r="G179" s="8"/>
       <c r="H179" s="8"/>
       <c r="I179" s="8"/>
-      <c r="J179" s="8"/>
+      <c r="J179" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="180" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B180" s="8"/>
-      <c r="C180" s="8"/>
-      <c r="D180" s="8"/>
-      <c r="E180" s="8"/>
-      <c r="F180" s="8"/>
+      <c r="B180" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C180" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D180" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E180" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="F180" s="8" t="s">
+        <v>188</v>
+      </c>
       <c r="G180" s="8"/>
       <c r="H180" s="8"/>
       <c r="I180" s="8"/>
-      <c r="J180" s="8"/>
+      <c r="J180" s="8" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="181" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B181" s="8"/>
-      <c r="C181" s="8"/>
-      <c r="D181" s="8"/>
-      <c r="E181" s="8"/>
-      <c r="F181" s="8"/>
+      <c r="B181" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C181" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D181" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E181" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="F181" s="8" t="s">
+        <v>94</v>
+      </c>
       <c r="G181" s="8"/>
       <c r="H181" s="8"/>
       <c r="I181" s="8"/>
-      <c r="J181" s="8"/>
+      <c r="J181" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="182" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B182" s="8"/>
-      <c r="C182" s="8"/>
-      <c r="D182" s="8"/>
-      <c r="E182" s="8"/>
-      <c r="F182" s="8"/>
+      <c r="B182" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C182" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D182" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E182" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="F182" s="8" t="s">
+        <v>189</v>
+      </c>
       <c r="G182" s="8"/>
       <c r="H182" s="8"/>
       <c r="I182" s="8"/>
-      <c r="J182" s="8"/>
+      <c r="J182" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="183" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B183" s="8"/>
-      <c r="C183" s="8"/>
-      <c r="D183" s="8"/>
-      <c r="E183" s="8"/>
-      <c r="F183" s="8"/>
+      <c r="B183" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C183" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D183" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E183" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="F183" s="8" t="s">
+        <v>135</v>
+      </c>
       <c r="G183" s="8"/>
       <c r="H183" s="8"/>
       <c r="I183" s="8"/>
-      <c r="J183" s="8"/>
+      <c r="J183" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="184" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B184" s="8"/>
-      <c r="C184" s="8"/>
-      <c r="D184" s="8"/>
-      <c r="E184" s="8"/>
-      <c r="F184" s="8"/>
+      <c r="B184" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C184" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D184" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="E184" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="F184" s="8" t="s">
+        <v>190</v>
+      </c>
       <c r="G184" s="8"/>
       <c r="H184" s="8"/>
       <c r="I184" s="8"/>
-      <c r="J184" s="8"/>
+      <c r="J184" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="185" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B185" s="8"/>
-      <c r="C185" s="8"/>
-      <c r="D185" s="8"/>
-      <c r="E185" s="8"/>
-      <c r="F185" s="8"/>
+      <c r="B185" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C185" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D185" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="E185" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="F185" s="8" t="s">
+        <v>191</v>
+      </c>
       <c r="G185" s="8"/>
       <c r="H185" s="8"/>
       <c r="I185" s="8"/>
-      <c r="J185" s="8"/>
+      <c r="J185" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="186" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B186" s="8"/>
-      <c r="C186" s="8"/>
-      <c r="D186" s="8"/>
-      <c r="E186" s="8"/>
-      <c r="F186" s="8"/>
+      <c r="B186" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C186" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D186" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="E186" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="F186" s="8" t="s">
+        <v>49</v>
+      </c>
       <c r="G186" s="8"/>
       <c r="H186" s="8"/>
       <c r="I186" s="8"/>
-      <c r="J186" s="8"/>
+      <c r="J186" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="187" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B187" s="8"/>
-      <c r="C187" s="8"/>
-      <c r="D187" s="8"/>
-      <c r="E187" s="8"/>
-      <c r="F187" s="8"/>
+      <c r="B187" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C187" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D187" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="E187" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="F187" s="8" t="s">
+        <v>192</v>
+      </c>
       <c r="G187" s="8"/>
       <c r="H187" s="8"/>
       <c r="I187" s="8"/>
-      <c r="J187" s="8"/>
+      <c r="J187" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="188" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B188" s="8"/>
-      <c r="C188" s="8"/>
-      <c r="D188" s="8"/>
-      <c r="E188" s="8"/>
-      <c r="F188" s="8"/>
+      <c r="B188" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C188" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D188" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="E188" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="F188" s="8" t="s">
+        <v>193</v>
+      </c>
       <c r="G188" s="8"/>
       <c r="H188" s="8"/>
       <c r="I188" s="8"/>
-      <c r="J188" s="8"/>
+      <c r="J188" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="189" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B189" s="8"/>
-      <c r="C189" s="8"/>
-      <c r="D189" s="8"/>
-      <c r="E189" s="8"/>
-      <c r="F189" s="8"/>
+      <c r="B189" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C189" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D189" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="E189" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="F189" s="8" t="s">
+        <v>194</v>
+      </c>
       <c r="G189" s="8"/>
       <c r="H189" s="8"/>
       <c r="I189" s="8"/>
-      <c r="J189" s="8"/>
+      <c r="J189" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="190" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B190" s="8"/>
-      <c r="C190" s="8"/>
-      <c r="D190" s="8"/>
-      <c r="E190" s="8"/>
-      <c r="F190" s="8"/>
+      <c r="B190" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C190" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D190" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="E190" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="F190" s="8" t="s">
+        <v>195</v>
+      </c>
       <c r="G190" s="8"/>
       <c r="H190" s="8"/>
       <c r="I190" s="8"/>
-      <c r="J190" s="8"/>
+      <c r="J190" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="191" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B191" s="8"/>
-      <c r="C191" s="8"/>
-      <c r="D191" s="8"/>
-      <c r="E191" s="8"/>
-      <c r="F191" s="8"/>
+      <c r="B191" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C191" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D191" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="E191" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="F191" s="8" t="s">
+        <v>196</v>
+      </c>
       <c r="G191" s="8"/>
       <c r="H191" s="8"/>
       <c r="I191" s="8"/>
-      <c r="J191" s="8"/>
+      <c r="J191" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="192" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B192" s="8"/>
-      <c r="C192" s="8"/>
-      <c r="D192" s="8"/>
-      <c r="E192" s="8"/>
-      <c r="F192" s="8"/>
+      <c r="B192" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C192" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D192" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="E192" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="F192" s="8" t="s">
+        <v>197</v>
+      </c>
       <c r="G192" s="8"/>
       <c r="H192" s="8"/>
       <c r="I192" s="8"/>
-      <c r="J192" s="8"/>
+      <c r="J192" s="8" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="193" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B193" s="8"/>
-      <c r="C193" s="8"/>
-      <c r="D193" s="8"/>
-      <c r="E193" s="8"/>
-      <c r="F193" s="8"/>
+      <c r="B193" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C193" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D193" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="E193" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="F193" s="8" t="s">
+        <v>198</v>
+      </c>
       <c r="G193" s="8"/>
       <c r="H193" s="8"/>
       <c r="I193" s="8"/>
-      <c r="J193" s="8"/>
+      <c r="J193" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="194" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F194" s="8"/>
+      <c r="B194" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C194" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D194" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="E194" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="F194" s="8" t="s">
+        <v>199</v>
+      </c>
       <c r="G194" s="8"/>
       <c r="H194" s="8"/>
       <c r="I194" s="8"/>
-    </row>
-    <row r="195" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F195" s="8"/>
+      <c r="J194" s="8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="195" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B195" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C195" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D195" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="E195" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="F195" s="8" t="s">
+        <v>200</v>
+      </c>
       <c r="G195" s="8"/>
       <c r="H195" s="8"/>
       <c r="I195" s="8"/>
+      <c r="J195" s="8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="196" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B196" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C196" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D196" s="8" t="n">
+        <v>17</v>
+      </c>
+      <c r="E196" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="F196" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="G196" s="8"/>
+      <c r="H196" s="8"/>
+      <c r="I196" s="8"/>
+      <c r="J196" s="8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="197" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B197" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C197" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D197" s="8" t="n">
+        <v>17</v>
+      </c>
+      <c r="E197" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="F197" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="G197" s="8"/>
+      <c r="H197" s="8"/>
+      <c r="I197" s="8"/>
+      <c r="J197" s="8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="198" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B198" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C198" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D198" s="8" t="n">
+        <v>17</v>
+      </c>
+      <c r="E198" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="F198" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="G198" s="8"/>
+      <c r="H198" s="8"/>
+      <c r="I198" s="8"/>
+      <c r="J198" s="8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="199" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B199" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C199" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D199" s="8" t="n">
+        <v>17</v>
+      </c>
+      <c r="E199" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="F199" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="G199" s="8"/>
+      <c r="H199" s="8"/>
+      <c r="I199" s="8"/>
+      <c r="J199" s="8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="200" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B200" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C200" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D200" s="8" t="n">
+        <v>18</v>
+      </c>
+      <c r="E200" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="F200" s="8" t="s">
+        <v>205</v>
+      </c>
+      <c r="G200" s="8"/>
+      <c r="H200" s="8"/>
+      <c r="I200" s="8"/>
+      <c r="J200" s="8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="201" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B201" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C201" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D201" s="8" t="n">
+        <v>18</v>
+      </c>
+      <c r="E201" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="F201" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="G201" s="8"/>
+      <c r="H201" s="8"/>
+      <c r="I201" s="8"/>
+      <c r="J201" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="202" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B202" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C202" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D202" s="8" t="n">
+        <v>18</v>
+      </c>
+      <c r="E202" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="F202" s="8" t="s">
+        <v>207</v>
+      </c>
+      <c r="G202" s="8"/>
+      <c r="H202" s="8"/>
+      <c r="I202" s="8"/>
+      <c r="J202" s="8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="203" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B203" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C203" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D203" s="8" t="n">
+        <v>18</v>
+      </c>
+      <c r="E203" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="F203" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="G203" s="8"/>
+      <c r="H203" s="8"/>
+      <c r="I203" s="8"/>
+      <c r="J203" s="8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="204" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B204" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C204" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D204" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="E204" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="F204" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="G204" s="8"/>
+      <c r="H204" s="8"/>
+      <c r="I204" s="8"/>
+      <c r="J204" s="8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="205" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B205" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C205" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D205" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="E205" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="F205" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="G205" s="8"/>
+      <c r="H205" s="8"/>
+      <c r="I205" s="8"/>
+      <c r="J205" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="206" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B206" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C206" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D206" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="E206" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="F206" s="8" t="s">
+        <v>211</v>
+      </c>
+      <c r="G206" s="8"/>
+      <c r="H206" s="8"/>
+      <c r="I206" s="8"/>
+      <c r="J206" s="8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="207" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B207" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C207" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D207" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="E207" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="F207" s="8" t="s">
+        <v>212</v>
+      </c>
+      <c r="G207" s="8"/>
+      <c r="H207" s="8"/>
+      <c r="I207" s="8"/>
+      <c r="J207" s="8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="208" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B208" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C208" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D208" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="E208" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="F208" s="8" t="s">
+        <v>213</v>
+      </c>
+      <c r="G208" s="8"/>
+      <c r="H208" s="8"/>
+      <c r="I208" s="8"/>
+      <c r="J208" s="8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="209" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B209" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C209" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D209" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="E209" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="F209" s="8" t="s">
+        <v>214</v>
+      </c>
+      <c r="G209" s="8"/>
+      <c r="H209" s="8"/>
+      <c r="I209" s="8"/>
+      <c r="J209" s="8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="210" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B210" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C210" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D210" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="E210" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="F210" s="8" t="s">
+        <v>215</v>
+      </c>
+      <c r="G210" s="8"/>
+      <c r="H210" s="8"/>
+      <c r="I210" s="8"/>
+      <c r="J210" s="8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="211" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B211" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C211" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D211" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="E211" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="F211" s="8" t="s">
+        <v>216</v>
+      </c>
+      <c r="G211" s="8"/>
+      <c r="H211" s="8"/>
+      <c r="I211" s="8"/>
+      <c r="J211" s="8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="212" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B212" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C212" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D212" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E212" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F212" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="G212" s="8"/>
+      <c r="H212" s="8"/>
+      <c r="I212" s="8"/>
+      <c r="J212" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="213" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B213" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C213" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D213" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E213" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F213" s="8" t="s">
+        <v>218</v>
+      </c>
+      <c r="G213" s="8"/>
+      <c r="H213" s="8"/>
+      <c r="I213" s="8"/>
+      <c r="J213" s="8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="214" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B214" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C214" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D214" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E214" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F214" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="G214" s="8"/>
+      <c r="H214" s="8"/>
+      <c r="I214" s="8"/>
+      <c r="J214" s="8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="215" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B215" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C215" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D215" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E215" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F215" s="8" t="s">
+        <v>220</v>
+      </c>
+      <c r="G215" s="8"/>
+      <c r="H215" s="8"/>
+      <c r="I215" s="8"/>
+      <c r="J215" s="8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="216" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B216" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C216" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D216" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E216" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F216" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="G216" s="8"/>
+      <c r="H216" s="8"/>
+      <c r="I216" s="8"/>
+      <c r="J216" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="217" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B217" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C217" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D217" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E217" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F217" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="G217" s="8"/>
+      <c r="H217" s="8"/>
+      <c r="I217" s="8"/>
+      <c r="J217" s="8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="218" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B218" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C218" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D218" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E218" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F218" s="8" t="s">
+        <v>223</v>
+      </c>
+      <c r="G218" s="8"/>
+      <c r="H218" s="8"/>
+      <c r="I218" s="8"/>
+      <c r="J218" s="8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="219" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B219" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C219" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D219" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E219" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F219" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="G219" s="8"/>
+      <c r="H219" s="8"/>
+      <c r="I219" s="8"/>
+      <c r="J219" s="8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="220" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B220" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C220" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D220" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="E220" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F220" s="8" t="s">
+        <v>225</v>
+      </c>
+      <c r="G220" s="8"/>
+      <c r="H220" s="8"/>
+      <c r="I220" s="8"/>
+      <c r="J220" s="8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="221" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B221" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C221" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D221" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="E221" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F221" s="8" t="s">
+        <v>226</v>
+      </c>
+      <c r="G221" s="8"/>
+      <c r="H221" s="8"/>
+      <c r="I221" s="8"/>
+      <c r="J221" s="8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="222" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B222" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C222" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D222" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="E222" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F222" s="8" t="s">
+        <v>227</v>
+      </c>
+      <c r="G222" s="8"/>
+      <c r="H222" s="8"/>
+      <c r="I222" s="8"/>
+      <c r="J222" s="8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="223" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B223" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C223" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D223" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="E223" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F223" s="8" t="s">
+        <v>228</v>
+      </c>
+      <c r="G223" s="8"/>
+      <c r="H223" s="8"/>
+      <c r="I223" s="8"/>
+      <c r="J223" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="224" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B224" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C224" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D224" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="E224" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F224" s="8" t="s">
+        <v>229</v>
+      </c>
+      <c r="G224" s="8"/>
+      <c r="H224" s="8"/>
+      <c r="I224" s="8"/>
+      <c r="J224" s="8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="225" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B225" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C225" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D225" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="E225" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F225" s="8" t="s">
+        <v>230</v>
+      </c>
+      <c r="G225" s="8"/>
+      <c r="H225" s="8"/>
+      <c r="I225" s="8"/>
+      <c r="J225" s="8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="226" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B226" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C226" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D226" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="E226" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F226" s="8" t="s">
+        <v>231</v>
+      </c>
+      <c r="G226" s="8"/>
+      <c r="H226" s="8"/>
+      <c r="I226" s="8"/>
+      <c r="J226" s="8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="227" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B227" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C227" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D227" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="E227" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F227" s="8" t="s">
+        <v>232</v>
+      </c>
+      <c r="G227" s="8"/>
+      <c r="H227" s="8"/>
+      <c r="I227" s="8"/>
+      <c r="J227" s="8" t="s">
+        <v>17</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="193">

--- a/documentación/PRSC/Dailys.xlsx
+++ b/documentación/PRSC/Dailys.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="903" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="903" uniqueCount="231">
   <si>
     <t xml:space="preserve">Daily</t>
   </si>
@@ -73,9 +73,6 @@
     <t xml:space="preserve">Armar el GANTT</t>
   </si>
   <si>
-    <t xml:space="preserve">En Proceso</t>
-  </si>
-  <si>
     <t xml:space="preserve">Bruno Cabrera</t>
   </si>
   <si>
@@ -83,9 +80,6 @@
   </si>
   <si>
     <t xml:space="preserve">Dibujar los wireframes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Proceso</t>
   </si>
   <si>
     <t xml:space="preserve">Instalar lo que necesita el proyecto</t>
@@ -1401,15 +1395,15 @@
       <c r="H6" s="8"/>
       <c r="I6" s="8"/>
       <c r="J6" s="8" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="7" t="s">
         <v>18</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>19</v>
       </c>
       <c r="D7" s="8" t="n">
         <v>2</v>
@@ -1418,13 +1412,13 @@
         <v>4</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G7" s="8"/>
       <c r="H7" s="8"/>
       <c r="I7" s="8"/>
       <c r="J7" s="8" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1441,13 +1435,13 @@
         <v>4</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G8" s="8"/>
       <c r="H8" s="8"/>
       <c r="I8" s="8"/>
       <c r="J8" s="8" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1464,7 +1458,7 @@
         <v>4</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G9" s="8"/>
       <c r="H9" s="8"/>
@@ -1487,7 +1481,7 @@
         <v>4</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G10" s="8"/>
       <c r="H10" s="8"/>
@@ -1498,10 +1492,10 @@
     </row>
     <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" s="7" t="s">
         <v>18</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>19</v>
       </c>
       <c r="D11" s="8" t="n">
         <v>3</v>
@@ -1510,13 +1504,13 @@
         <v>4</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G11" s="8"/>
       <c r="H11" s="8"/>
       <c r="I11" s="8"/>
       <c r="J11" s="8" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1533,7 +1527,7 @@
         <v>4</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G12" s="8"/>
       <c r="H12" s="8"/>
@@ -1556,7 +1550,7 @@
         <v>4</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G13" s="8"/>
       <c r="H13" s="8"/>
@@ -1579,21 +1573,21 @@
         <v>4</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G14" s="8"/>
       <c r="H14" s="8"/>
       <c r="I14" s="8"/>
       <c r="J14" s="8" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" s="7" t="s">
         <v>18</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>19</v>
       </c>
       <c r="D15" s="8" t="n">
         <v>9</v>
@@ -1602,7 +1596,7 @@
         <v>4</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G15" s="8"/>
       <c r="H15" s="8"/>
@@ -1625,7 +1619,7 @@
         <v>4</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G16" s="8"/>
       <c r="H16" s="8"/>
@@ -1648,7 +1642,7 @@
         <v>4</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G17" s="8"/>
       <c r="H17" s="8"/>
@@ -1671,7 +1665,7 @@
         <v>4</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G18" s="8"/>
       <c r="H18" s="8"/>
@@ -1682,10 +1676,10 @@
     </row>
     <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C19" s="7" t="s">
         <v>18</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>19</v>
       </c>
       <c r="D19" s="8" t="n">
         <v>10</v>
@@ -1694,7 +1688,7 @@
         <v>4</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G19" s="8"/>
       <c r="H19" s="8"/>
@@ -1717,7 +1711,7 @@
         <v>4</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G20" s="8"/>
       <c r="H20" s="8"/>
@@ -1740,7 +1734,7 @@
         <v>4</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G21" s="8"/>
       <c r="H21" s="8"/>
@@ -1763,7 +1757,7 @@
         <v>4</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G22" s="8"/>
       <c r="H22" s="8"/>
@@ -1774,10 +1768,10 @@
     </row>
     <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C23" s="7" t="s">
         <v>18</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>19</v>
       </c>
       <c r="D23" s="8" t="n">
         <v>16</v>
@@ -1786,7 +1780,7 @@
         <v>4</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G23" s="8"/>
       <c r="H23" s="8"/>
@@ -1809,7 +1803,7 @@
         <v>4</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G24" s="8"/>
       <c r="H24" s="8"/>
@@ -1832,13 +1826,13 @@
         <v>4</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G25" s="8"/>
       <c r="H25" s="8"/>
       <c r="I25" s="8"/>
       <c r="J25" s="8" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1855,7 +1849,7 @@
         <v>4</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G26" s="8"/>
       <c r="H26" s="8"/>
@@ -1866,10 +1860,10 @@
     </row>
     <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C27" s="7" t="s">
         <v>18</v>
-      </c>
-      <c r="C27" s="7" t="s">
-        <v>19</v>
       </c>
       <c r="D27" s="8" t="n">
         <v>17</v>
@@ -1878,13 +1872,13 @@
         <v>4</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G27" s="8"/>
       <c r="H27" s="8"/>
       <c r="I27" s="8"/>
       <c r="J27" s="8" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1901,7 +1895,7 @@
         <v>4</v>
       </c>
       <c r="F28" s="8" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G28" s="8"/>
       <c r="H28" s="8"/>
@@ -1924,7 +1918,7 @@
         <v>4</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G29" s="8"/>
       <c r="H29" s="8"/>
@@ -1947,21 +1941,21 @@
         <v>4</v>
       </c>
       <c r="F30" s="8" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G30" s="8"/>
       <c r="H30" s="8"/>
       <c r="I30" s="8"/>
       <c r="J30" s="8" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C31" s="7" t="s">
         <v>18</v>
-      </c>
-      <c r="C31" s="7" t="s">
-        <v>19</v>
       </c>
       <c r="D31" s="8" t="n">
         <v>23</v>
@@ -1970,7 +1964,7 @@
         <v>4</v>
       </c>
       <c r="F31" s="8" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G31" s="8"/>
       <c r="H31" s="8"/>
@@ -1993,7 +1987,7 @@
         <v>4</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G32" s="8"/>
       <c r="H32" s="8"/>
@@ -2016,7 +2010,7 @@
         <v>4</v>
       </c>
       <c r="F33" s="8" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G33" s="8"/>
       <c r="H33" s="8"/>
@@ -2039,7 +2033,7 @@
         <v>4</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G34" s="8"/>
       <c r="H34" s="8"/>
@@ -2050,10 +2044,10 @@
     </row>
     <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C35" s="7" t="s">
         <v>18</v>
-      </c>
-      <c r="C35" s="7" t="s">
-        <v>19</v>
       </c>
       <c r="D35" s="8" t="n">
         <v>24</v>
@@ -2062,7 +2056,7 @@
         <v>4</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G35" s="8"/>
       <c r="H35" s="8"/>
@@ -2085,7 +2079,7 @@
         <v>4</v>
       </c>
       <c r="F36" s="8" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G36" s="8"/>
       <c r="H36" s="8"/>
@@ -2108,7 +2102,7 @@
         <v>4</v>
       </c>
       <c r="F37" s="8" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G37" s="8"/>
       <c r="H37" s="8"/>
@@ -2131,7 +2125,7 @@
         <v>4</v>
       </c>
       <c r="F38" s="8" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G38" s="8"/>
       <c r="H38" s="8"/>
@@ -2142,10 +2136,10 @@
     </row>
     <row r="39" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C39" s="7" t="s">
         <v>18</v>
-      </c>
-      <c r="C39" s="7" t="s">
-        <v>19</v>
       </c>
       <c r="D39" s="8" t="n">
         <v>30</v>
@@ -2154,7 +2148,7 @@
         <v>4</v>
       </c>
       <c r="F39" s="8" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G39" s="8"/>
       <c r="H39" s="8"/>
@@ -2177,7 +2171,7 @@
         <v>5</v>
       </c>
       <c r="F40" s="8" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G40" s="8"/>
       <c r="H40" s="8"/>
@@ -2200,7 +2194,7 @@
         <v>5</v>
       </c>
       <c r="F41" s="8" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G41" s="8"/>
       <c r="H41" s="8"/>
@@ -2223,7 +2217,7 @@
         <v>5</v>
       </c>
       <c r="F42" s="8" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G42" s="8"/>
       <c r="H42" s="8"/>
@@ -2234,10 +2228,10 @@
     </row>
     <row r="43" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B43" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C43" s="7" t="s">
         <v>18</v>
-      </c>
-      <c r="C43" s="7" t="s">
-        <v>19</v>
       </c>
       <c r="D43" s="8" t="n">
         <v>1</v>
@@ -2246,7 +2240,7 @@
         <v>5</v>
       </c>
       <c r="F43" s="8" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G43" s="8"/>
       <c r="H43" s="8"/>
@@ -2269,13 +2263,13 @@
         <v>5</v>
       </c>
       <c r="F44" s="8" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G44" s="8"/>
       <c r="H44" s="8"/>
       <c r="I44" s="8"/>
       <c r="J44" s="8" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2292,7 +2286,7 @@
         <v>5</v>
       </c>
       <c r="F45" s="8" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G45" s="8"/>
       <c r="H45" s="8"/>
@@ -2315,7 +2309,7 @@
         <v>5</v>
       </c>
       <c r="F46" s="8" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G46" s="8"/>
       <c r="H46" s="8"/>
@@ -2326,10 +2320,10 @@
     </row>
     <row r="47" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B47" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C47" s="7" t="s">
         <v>18</v>
-      </c>
-      <c r="C47" s="7" t="s">
-        <v>19</v>
       </c>
       <c r="D47" s="8" t="n">
         <v>7</v>
@@ -2338,7 +2332,7 @@
         <v>5</v>
       </c>
       <c r="F47" s="8" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G47" s="8"/>
       <c r="H47" s="8"/>
@@ -2361,7 +2355,7 @@
         <v>5</v>
       </c>
       <c r="F48" s="8" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G48" s="8"/>
       <c r="H48" s="8"/>
@@ -2384,13 +2378,13 @@
         <v>5</v>
       </c>
       <c r="F49" s="8" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G49" s="8"/>
       <c r="H49" s="8"/>
       <c r="I49" s="8"/>
       <c r="J49" s="8" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2407,7 +2401,7 @@
         <v>5</v>
       </c>
       <c r="F50" s="8" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G50" s="8"/>
       <c r="H50" s="8"/>
@@ -2418,10 +2412,10 @@
     </row>
     <row r="51" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B51" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C51" s="7" t="s">
         <v>18</v>
-      </c>
-      <c r="C51" s="7" t="s">
-        <v>19</v>
       </c>
       <c r="D51" s="8" t="n">
         <v>8</v>
@@ -2430,7 +2424,7 @@
         <v>5</v>
       </c>
       <c r="F51" s="8" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G51" s="8"/>
       <c r="H51" s="8"/>
@@ -2453,7 +2447,7 @@
         <v>5</v>
       </c>
       <c r="F52" s="8" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G52" s="8"/>
       <c r="H52" s="8"/>
@@ -2476,13 +2470,13 @@
         <v>5</v>
       </c>
       <c r="F53" s="8" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G53" s="8"/>
       <c r="H53" s="8"/>
       <c r="I53" s="8"/>
       <c r="J53" s="8" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2499,7 +2493,7 @@
         <v>5</v>
       </c>
       <c r="F54" s="8" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G54" s="8"/>
       <c r="H54" s="8"/>
@@ -2510,10 +2504,10 @@
     </row>
     <row r="55" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B55" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C55" s="7" t="s">
         <v>18</v>
-      </c>
-      <c r="C55" s="7" t="s">
-        <v>19</v>
       </c>
       <c r="D55" s="8" t="n">
         <v>14</v>
@@ -2522,13 +2516,13 @@
         <v>5</v>
       </c>
       <c r="F55" s="8" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G55" s="8"/>
       <c r="H55" s="8"/>
       <c r="I55" s="8"/>
       <c r="J55" s="8" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2545,7 +2539,7 @@
         <v>5</v>
       </c>
       <c r="F56" s="8" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G56" s="8"/>
       <c r="H56" s="8"/>
@@ -2568,7 +2562,7 @@
         <v>5</v>
       </c>
       <c r="F57" s="8" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G57" s="8"/>
       <c r="H57" s="8"/>
@@ -2591,21 +2585,21 @@
         <v>5</v>
       </c>
       <c r="F58" s="8" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G58" s="8"/>
       <c r="H58" s="8"/>
       <c r="I58" s="8"/>
       <c r="J58" s="8" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B59" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C59" s="7" t="s">
         <v>18</v>
-      </c>
-      <c r="C59" s="7" t="s">
-        <v>19</v>
       </c>
       <c r="D59" s="8" t="n">
         <v>15</v>
@@ -2614,7 +2608,7 @@
         <v>5</v>
       </c>
       <c r="F59" s="8" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G59" s="8"/>
       <c r="H59" s="8"/>
@@ -2637,13 +2631,13 @@
         <v>5</v>
       </c>
       <c r="F60" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G60" s="8"/>
       <c r="H60" s="8"/>
       <c r="I60" s="8"/>
       <c r="J60" s="8" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2660,7 +2654,7 @@
         <v>5</v>
       </c>
       <c r="F61" s="8" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="G61" s="8"/>
       <c r="H61" s="8"/>
@@ -2683,7 +2677,7 @@
         <v>5</v>
       </c>
       <c r="F62" s="8" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="G62" s="8"/>
       <c r="H62" s="8"/>
@@ -2694,10 +2688,10 @@
     </row>
     <row r="63" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B63" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C63" s="7" t="s">
         <v>18</v>
-      </c>
-      <c r="C63" s="7" t="s">
-        <v>19</v>
       </c>
       <c r="D63" s="8" t="n">
         <v>21</v>
@@ -2706,7 +2700,7 @@
         <v>5</v>
       </c>
       <c r="F63" s="8" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="G63" s="8"/>
       <c r="H63" s="8"/>
@@ -2729,7 +2723,7 @@
         <v>5</v>
       </c>
       <c r="F64" s="8" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="G64" s="8"/>
       <c r="H64" s="8"/>
@@ -2752,7 +2746,7 @@
         <v>5</v>
       </c>
       <c r="F65" s="8" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G65" s="8"/>
       <c r="H65" s="8"/>
@@ -2775,7 +2769,7 @@
         <v>5</v>
       </c>
       <c r="F66" s="8" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="G66" s="8"/>
       <c r="H66" s="8"/>
@@ -2786,10 +2780,10 @@
     </row>
     <row r="67" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B67" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C67" s="7" t="s">
         <v>18</v>
-      </c>
-      <c r="C67" s="7" t="s">
-        <v>19</v>
       </c>
       <c r="D67" s="8" t="n">
         <v>22</v>
@@ -2798,13 +2792,13 @@
         <v>5</v>
       </c>
       <c r="F67" s="8" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G67" s="8"/>
       <c r="H67" s="8"/>
       <c r="I67" s="8"/>
       <c r="J67" s="8" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2821,7 +2815,7 @@
         <v>5</v>
       </c>
       <c r="F68" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G68" s="8"/>
       <c r="H68" s="8"/>
@@ -2844,7 +2838,7 @@
         <v>5</v>
       </c>
       <c r="F69" s="8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G69" s="8"/>
       <c r="H69" s="8"/>
@@ -2867,7 +2861,7 @@
         <v>5</v>
       </c>
       <c r="F70" s="8" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G70" s="8"/>
       <c r="H70" s="8"/>
@@ -2878,10 +2872,10 @@
     </row>
     <row r="71" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B71" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C71" s="7" t="s">
         <v>18</v>
-      </c>
-      <c r="C71" s="7" t="s">
-        <v>19</v>
       </c>
       <c r="D71" s="8" t="n">
         <v>28</v>
@@ -2890,7 +2884,7 @@
         <v>5</v>
       </c>
       <c r="F71" s="8" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G71" s="8"/>
       <c r="H71" s="8"/>
@@ -2913,7 +2907,7 @@
         <v>5</v>
       </c>
       <c r="F72" s="8" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="G72" s="8"/>
       <c r="H72" s="8"/>
@@ -2936,7 +2930,7 @@
         <v>5</v>
       </c>
       <c r="F73" s="8" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="G73" s="8"/>
       <c r="H73" s="8"/>
@@ -2959,7 +2953,7 @@
         <v>5</v>
       </c>
       <c r="F74" s="8" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G74" s="8"/>
       <c r="H74" s="8"/>
@@ -2970,10 +2964,10 @@
     </row>
     <row r="75" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B75" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C75" s="7" t="s">
         <v>18</v>
-      </c>
-      <c r="C75" s="7" t="s">
-        <v>19</v>
       </c>
       <c r="D75" s="8" t="n">
         <v>29</v>
@@ -2982,7 +2976,7 @@
         <v>5</v>
       </c>
       <c r="F75" s="8" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G75" s="8"/>
       <c r="H75" s="8"/>
@@ -3005,13 +2999,13 @@
         <v>6</v>
       </c>
       <c r="F76" s="8" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="G76" s="8"/>
       <c r="H76" s="8"/>
       <c r="I76" s="8"/>
       <c r="J76" s="8" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3028,7 +3022,7 @@
         <v>6</v>
       </c>
       <c r="F77" s="8" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G77" s="8"/>
       <c r="H77" s="8"/>
@@ -3051,21 +3045,21 @@
         <v>6</v>
       </c>
       <c r="F78" s="8" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="G78" s="8"/>
       <c r="H78" s="8"/>
       <c r="I78" s="8"/>
       <c r="J78" s="8" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B79" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C79" s="7" t="s">
         <v>18</v>
-      </c>
-      <c r="C79" s="7" t="s">
-        <v>19</v>
       </c>
       <c r="D79" s="8" t="n">
         <v>4</v>
@@ -3074,7 +3068,7 @@
         <v>6</v>
       </c>
       <c r="F79" s="8" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="G79" s="8"/>
       <c r="H79" s="8"/>
@@ -3097,7 +3091,7 @@
         <v>6</v>
       </c>
       <c r="F80" s="8" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="G80" s="8"/>
       <c r="H80" s="8"/>
@@ -3120,13 +3114,13 @@
         <v>6</v>
       </c>
       <c r="F81" s="8" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="G81" s="8"/>
       <c r="H81" s="8"/>
       <c r="I81" s="8"/>
       <c r="J81" s="8" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3143,7 +3137,7 @@
         <v>6</v>
       </c>
       <c r="F82" s="8" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="G82" s="8"/>
       <c r="H82" s="8"/>
@@ -3154,10 +3148,10 @@
     </row>
     <row r="83" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B83" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C83" s="7" t="s">
         <v>18</v>
-      </c>
-      <c r="C83" s="7" t="s">
-        <v>19</v>
       </c>
       <c r="D83" s="8" t="n">
         <v>5</v>
@@ -3166,7 +3160,7 @@
         <v>6</v>
       </c>
       <c r="F83" s="8" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G83" s="8"/>
       <c r="H83" s="8"/>
@@ -3189,13 +3183,13 @@
         <v>6</v>
       </c>
       <c r="F84" s="8" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="G84" s="8"/>
       <c r="H84" s="8"/>
       <c r="I84" s="8"/>
       <c r="J84" s="8" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3212,7 +3206,7 @@
         <v>6</v>
       </c>
       <c r="F85" s="8" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="G85" s="8"/>
       <c r="H85" s="8"/>
@@ -3235,21 +3229,21 @@
         <v>6</v>
       </c>
       <c r="F86" s="8" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G86" s="8"/>
       <c r="H86" s="8"/>
       <c r="I86" s="8"/>
       <c r="J86" s="8" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B87" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C87" s="7" t="s">
         <v>18</v>
-      </c>
-      <c r="C87" s="7" t="s">
-        <v>19</v>
       </c>
       <c r="D87" s="8" t="n">
         <v>11</v>
@@ -3258,7 +3252,7 @@
         <v>6</v>
       </c>
       <c r="F87" s="8" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="G87" s="8"/>
       <c r="H87" s="8"/>
@@ -3281,13 +3275,13 @@
         <v>6</v>
       </c>
       <c r="F88" s="8" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G88" s="8"/>
       <c r="H88" s="8"/>
       <c r="I88" s="8"/>
       <c r="J88" s="8" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3304,7 +3298,7 @@
         <v>6</v>
       </c>
       <c r="F89" s="8" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G89" s="8"/>
       <c r="H89" s="8"/>
@@ -3327,7 +3321,7 @@
         <v>6</v>
       </c>
       <c r="F90" s="8" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="G90" s="8"/>
       <c r="H90" s="8"/>
@@ -3338,10 +3332,10 @@
     </row>
     <row r="91" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B91" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C91" s="7" t="s">
         <v>18</v>
-      </c>
-      <c r="C91" s="7" t="s">
-        <v>19</v>
       </c>
       <c r="D91" s="8" t="n">
         <v>12</v>
@@ -3350,7 +3344,7 @@
         <v>6</v>
       </c>
       <c r="F91" s="8" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="G91" s="8"/>
       <c r="H91" s="8"/>
@@ -3373,13 +3367,13 @@
         <v>6</v>
       </c>
       <c r="F92" s="8" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="G92" s="8"/>
       <c r="H92" s="8"/>
       <c r="I92" s="8"/>
       <c r="J92" s="8" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3396,13 +3390,13 @@
         <v>6</v>
       </c>
       <c r="F93" s="8" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="G93" s="8"/>
       <c r="H93" s="8"/>
       <c r="I93" s="8"/>
       <c r="J93" s="8" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3419,7 +3413,7 @@
         <v>6</v>
       </c>
       <c r="F94" s="8" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G94" s="8"/>
       <c r="H94" s="8"/>
@@ -3430,10 +3424,10 @@
     </row>
     <row r="95" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B95" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C95" s="7" t="s">
         <v>18</v>
-      </c>
-      <c r="C95" s="7" t="s">
-        <v>19</v>
       </c>
       <c r="D95" s="8" t="n">
         <v>18</v>
@@ -3442,7 +3436,7 @@
         <v>6</v>
       </c>
       <c r="F95" s="8" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="G95" s="8"/>
       <c r="H95" s="8"/>
@@ -3465,7 +3459,7 @@
         <v>6</v>
       </c>
       <c r="F96" s="8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="G96" s="8"/>
       <c r="H96" s="8"/>
@@ -3488,13 +3482,13 @@
         <v>6</v>
       </c>
       <c r="F97" s="8" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G97" s="8"/>
       <c r="H97" s="8"/>
       <c r="I97" s="8"/>
       <c r="J97" s="8" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3511,7 +3505,7 @@
         <v>6</v>
       </c>
       <c r="F98" s="8" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G98" s="8"/>
       <c r="H98" s="8"/>
@@ -3522,10 +3516,10 @@
     </row>
     <row r="99" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B99" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C99" s="7" t="s">
         <v>18</v>
-      </c>
-      <c r="C99" s="7" t="s">
-        <v>19</v>
       </c>
       <c r="D99" s="8" t="n">
         <v>19</v>
@@ -3534,7 +3528,7 @@
         <v>6</v>
       </c>
       <c r="F99" s="8" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G99" s="8"/>
       <c r="H99" s="8"/>
@@ -3557,13 +3551,13 @@
         <v>6</v>
       </c>
       <c r="F100" s="8" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G100" s="8"/>
       <c r="H100" s="8"/>
       <c r="I100" s="8"/>
       <c r="J100" s="8" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3580,7 +3574,7 @@
         <v>6</v>
       </c>
       <c r="F101" s="8" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G101" s="8"/>
       <c r="H101" s="8"/>
@@ -3603,7 +3597,7 @@
         <v>6</v>
       </c>
       <c r="F102" s="8" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="G102" s="8"/>
       <c r="H102" s="8"/>
@@ -3614,10 +3608,10 @@
     </row>
     <row r="103" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B103" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C103" s="7" t="s">
         <v>18</v>
-      </c>
-      <c r="C103" s="7" t="s">
-        <v>19</v>
       </c>
       <c r="D103" s="8" t="n">
         <v>25</v>
@@ -3626,7 +3620,7 @@
         <v>6</v>
       </c>
       <c r="F103" s="8" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="G103" s="8"/>
       <c r="H103" s="8"/>
@@ -3649,7 +3643,7 @@
         <v>6</v>
       </c>
       <c r="F104" s="8" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="G104" s="8"/>
       <c r="H104" s="8"/>
@@ -3672,13 +3666,13 @@
         <v>6</v>
       </c>
       <c r="F105" s="8" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="G105" s="8"/>
       <c r="H105" s="8"/>
       <c r="I105" s="8"/>
       <c r="J105" s="8" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3695,7 +3689,7 @@
         <v>6</v>
       </c>
       <c r="F106" s="8" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="G106" s="8"/>
       <c r="H106" s="8"/>
@@ -3706,10 +3700,10 @@
     </row>
     <row r="107" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B107" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C107" s="7" t="s">
         <v>18</v>
-      </c>
-      <c r="C107" s="7" t="s">
-        <v>19</v>
       </c>
       <c r="D107" s="8" t="n">
         <v>26</v>
@@ -3718,7 +3712,7 @@
         <v>6</v>
       </c>
       <c r="F107" s="8" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G107" s="8"/>
       <c r="H107" s="8"/>
@@ -3741,13 +3735,13 @@
         <v>7</v>
       </c>
       <c r="F108" s="8" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="G108" s="8"/>
       <c r="H108" s="8"/>
       <c r="I108" s="8"/>
       <c r="J108" s="8" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3764,7 +3758,7 @@
         <v>7</v>
       </c>
       <c r="F109" s="8" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="G109" s="8"/>
       <c r="H109" s="8"/>
@@ -3787,7 +3781,7 @@
         <v>7</v>
       </c>
       <c r="F110" s="8" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="G110" s="8"/>
       <c r="H110" s="8"/>
@@ -3798,10 +3792,10 @@
     </row>
     <row r="111" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B111" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C111" s="7" t="s">
         <v>18</v>
-      </c>
-      <c r="C111" s="7" t="s">
-        <v>19</v>
       </c>
       <c r="D111" s="8" t="n">
         <v>2</v>
@@ -3810,13 +3804,13 @@
         <v>7</v>
       </c>
       <c r="F111" s="8" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="G111" s="8"/>
       <c r="H111" s="8"/>
       <c r="I111" s="8"/>
       <c r="J111" s="8" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3833,7 +3827,7 @@
         <v>7</v>
       </c>
       <c r="F112" s="8" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="G112" s="8"/>
       <c r="H112" s="8"/>
@@ -3856,7 +3850,7 @@
         <v>7</v>
       </c>
       <c r="F113" s="8" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G113" s="8"/>
       <c r="H113" s="8"/>
@@ -3879,7 +3873,7 @@
         <v>7</v>
       </c>
       <c r="F114" s="8" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G114" s="8"/>
       <c r="H114" s="8"/>
@@ -3890,10 +3884,10 @@
     </row>
     <row r="115" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B115" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C115" s="7" t="s">
         <v>18</v>
-      </c>
-      <c r="C115" s="7" t="s">
-        <v>19</v>
       </c>
       <c r="D115" s="8" t="n">
         <v>3</v>
@@ -3902,7 +3896,7 @@
         <v>7</v>
       </c>
       <c r="F115" s="8" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="G115" s="8"/>
       <c r="H115" s="8"/>
@@ -3925,7 +3919,7 @@
         <v>7</v>
       </c>
       <c r="F116" s="8" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G116" s="8"/>
       <c r="H116" s="8"/>
@@ -3948,7 +3942,7 @@
         <v>7</v>
       </c>
       <c r="F117" s="8" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G117" s="8"/>
       <c r="H117" s="8"/>
@@ -3971,7 +3965,7 @@
         <v>7</v>
       </c>
       <c r="F118" s="8" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="G118" s="8"/>
       <c r="H118" s="8"/>
@@ -3982,10 +3976,10 @@
     </row>
     <row r="119" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B119" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C119" s="7" t="s">
         <v>18</v>
-      </c>
-      <c r="C119" s="7" t="s">
-        <v>19</v>
       </c>
       <c r="D119" s="8" t="n">
         <v>9</v>
@@ -3994,7 +3988,7 @@
         <v>7</v>
       </c>
       <c r="F119" s="8" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G119" s="8"/>
       <c r="H119" s="8"/>
@@ -4017,7 +4011,7 @@
         <v>7</v>
       </c>
       <c r="F120" s="8" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="G120" s="8"/>
       <c r="H120" s="8"/>
@@ -4040,7 +4034,7 @@
         <v>7</v>
       </c>
       <c r="F121" s="8" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G121" s="8"/>
       <c r="H121" s="8"/>
@@ -4063,22 +4057,22 @@
         <v>7</v>
       </c>
       <c r="F122" s="8" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="G122" s="8"/>
       <c r="H122" s="8"/>
       <c r="I122" s="8"/>
       <c r="J122" s="8" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B123" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C123" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C123" s="7" t="s">
-        <v>19</v>
-      </c>
       <c r="D123" s="8" t="n">
         <v>10</v>
       </c>
@@ -4086,13 +4080,13 @@
         <v>7</v>
       </c>
       <c r="F123" s="8" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G123" s="8"/>
       <c r="H123" s="8"/>
       <c r="I123" s="8"/>
       <c r="J123" s="8" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4109,7 +4103,7 @@
         <v>7</v>
       </c>
       <c r="F124" s="8" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G124" s="8"/>
       <c r="H124" s="8"/>
@@ -4132,7 +4126,7 @@
         <v>7</v>
       </c>
       <c r="F125" s="8" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="G125" s="8"/>
       <c r="H125" s="8"/>
@@ -4155,7 +4149,7 @@
         <v>7</v>
       </c>
       <c r="F126" s="8" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="G126" s="8"/>
       <c r="H126" s="8"/>
@@ -4166,10 +4160,10 @@
     </row>
     <row r="127" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B127" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C127" s="7" t="s">
         <v>18</v>
-      </c>
-      <c r="C127" s="7" t="s">
-        <v>19</v>
       </c>
       <c r="D127" s="8" t="n">
         <v>16</v>
@@ -4178,7 +4172,7 @@
         <v>7</v>
       </c>
       <c r="F127" s="8" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G127" s="8"/>
       <c r="H127" s="8"/>
@@ -4201,13 +4195,13 @@
         <v>7</v>
       </c>
       <c r="F128" s="8" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="G128" s="8"/>
       <c r="H128" s="8"/>
       <c r="I128" s="8"/>
       <c r="J128" s="8" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4224,13 +4218,13 @@
         <v>7</v>
       </c>
       <c r="F129" s="8" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="G129" s="8"/>
       <c r="H129" s="8"/>
       <c r="I129" s="8"/>
       <c r="J129" s="8" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4247,7 +4241,7 @@
         <v>7</v>
       </c>
       <c r="F130" s="8" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="G130" s="8"/>
       <c r="H130" s="8"/>
@@ -4258,11 +4252,11 @@
     </row>
     <row r="131" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B131" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C131" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C131" s="7" t="s">
-        <v>19</v>
-      </c>
       <c r="D131" s="8" t="n">
         <v>17</v>
       </c>
@@ -4270,13 +4264,13 @@
         <v>7</v>
       </c>
       <c r="F131" s="8" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="G131" s="8"/>
       <c r="H131" s="8"/>
       <c r="I131" s="8"/>
       <c r="J131" s="8" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4293,7 +4287,7 @@
         <v>7</v>
       </c>
       <c r="F132" s="8" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G132" s="8"/>
       <c r="H132" s="8"/>
@@ -4316,7 +4310,7 @@
         <v>7</v>
       </c>
       <c r="F133" s="8" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="G133" s="8"/>
       <c r="H133" s="8"/>
@@ -4339,7 +4333,7 @@
         <v>7</v>
       </c>
       <c r="F134" s="8" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="G134" s="8"/>
       <c r="H134" s="8"/>
@@ -4350,10 +4344,10 @@
     </row>
     <row r="135" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B135" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C135" s="7" t="s">
         <v>18</v>
-      </c>
-      <c r="C135" s="7" t="s">
-        <v>19</v>
       </c>
       <c r="D135" s="8" t="n">
         <v>23</v>
@@ -4362,7 +4356,7 @@
         <v>7</v>
       </c>
       <c r="F135" s="8" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="G135" s="8"/>
       <c r="H135" s="8"/>
@@ -4385,7 +4379,7 @@
         <v>7</v>
       </c>
       <c r="F136" s="8" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G136" s="8"/>
       <c r="H136" s="8"/>
@@ -4408,7 +4402,7 @@
         <v>7</v>
       </c>
       <c r="F137" s="8" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="G137" s="8"/>
       <c r="H137" s="8"/>
@@ -4431,7 +4425,7 @@
         <v>7</v>
       </c>
       <c r="F138" s="8" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="G138" s="8"/>
       <c r="H138" s="8"/>
@@ -4442,10 +4436,10 @@
     </row>
     <row r="139" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B139" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C139" s="7" t="s">
         <v>18</v>
-      </c>
-      <c r="C139" s="7" t="s">
-        <v>19</v>
       </c>
       <c r="D139" s="8" t="n">
         <v>24</v>
@@ -4454,13 +4448,13 @@
         <v>7</v>
       </c>
       <c r="F139" s="8" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="G139" s="8"/>
       <c r="H139" s="8"/>
       <c r="I139" s="8"/>
       <c r="J139" s="8" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4477,13 +4471,13 @@
         <v>7</v>
       </c>
       <c r="F140" s="8" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="G140" s="8"/>
       <c r="H140" s="8"/>
       <c r="I140" s="8"/>
       <c r="J140" s="8" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4500,7 +4494,7 @@
         <v>7</v>
       </c>
       <c r="F141" s="8" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="G141" s="8"/>
       <c r="H141" s="8"/>
@@ -4523,7 +4517,7 @@
         <v>7</v>
       </c>
       <c r="F142" s="8" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="G142" s="8"/>
       <c r="H142" s="8"/>
@@ -4534,10 +4528,10 @@
     </row>
     <row r="143" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B143" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C143" s="7" t="s">
         <v>18</v>
-      </c>
-      <c r="C143" s="7" t="s">
-        <v>19</v>
       </c>
       <c r="D143" s="8" t="n">
         <v>30</v>
@@ -4546,7 +4540,7 @@
         <v>7</v>
       </c>
       <c r="F143" s="8" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="G143" s="8"/>
       <c r="H143" s="8"/>
@@ -4569,7 +4563,7 @@
         <v>7</v>
       </c>
       <c r="F144" s="8" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="G144" s="8"/>
       <c r="H144" s="8"/>
@@ -4592,7 +4586,7 @@
         <v>7</v>
       </c>
       <c r="F145" s="8" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="G145" s="8"/>
       <c r="H145" s="8"/>
@@ -4615,7 +4609,7 @@
         <v>7</v>
       </c>
       <c r="F146" s="8" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="G146" s="8"/>
       <c r="H146" s="8"/>
@@ -4626,10 +4620,10 @@
     </row>
     <row r="147" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B147" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C147" s="7" t="s">
         <v>18</v>
-      </c>
-      <c r="C147" s="7" t="s">
-        <v>19</v>
       </c>
       <c r="D147" s="8" t="n">
         <v>31</v>
@@ -4638,7 +4632,7 @@
         <v>7</v>
       </c>
       <c r="F147" s="8" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="G147" s="8"/>
       <c r="H147" s="8"/>
@@ -4661,7 +4655,7 @@
         <v>8</v>
       </c>
       <c r="F148" s="8" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="G148" s="8"/>
       <c r="H148" s="8"/>
@@ -4684,7 +4678,7 @@
         <v>8</v>
       </c>
       <c r="F149" s="8" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="G149" s="8"/>
       <c r="H149" s="8"/>
@@ -4707,7 +4701,7 @@
         <v>8</v>
       </c>
       <c r="F150" s="8" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="G150" s="8"/>
       <c r="H150" s="8"/>
@@ -4718,10 +4712,10 @@
     </row>
     <row r="151" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B151" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C151" s="7" t="s">
         <v>18</v>
-      </c>
-      <c r="C151" s="7" t="s">
-        <v>19</v>
       </c>
       <c r="D151" s="8" t="n">
         <v>6</v>
@@ -4730,13 +4724,13 @@
         <v>8</v>
       </c>
       <c r="F151" s="8" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="G151" s="8"/>
       <c r="H151" s="8"/>
       <c r="I151" s="8"/>
       <c r="J151" s="8" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4753,7 +4747,7 @@
         <v>8</v>
       </c>
       <c r="F152" s="8" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="G152" s="8"/>
       <c r="H152" s="8"/>
@@ -4776,7 +4770,7 @@
         <v>8</v>
       </c>
       <c r="F153" s="8" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="G153" s="8"/>
       <c r="H153" s="8"/>
@@ -4799,7 +4793,7 @@
         <v>8</v>
       </c>
       <c r="F154" s="8" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="G154" s="8"/>
       <c r="H154" s="8"/>
@@ -4810,11 +4804,11 @@
     </row>
     <row r="155" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B155" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C155" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C155" s="7" t="s">
-        <v>19</v>
-      </c>
       <c r="D155" s="8" t="n">
         <v>7</v>
       </c>
@@ -4822,7 +4816,7 @@
         <v>8</v>
       </c>
       <c r="F155" s="8" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="G155" s="8"/>
       <c r="H155" s="8"/>
@@ -4845,7 +4839,7 @@
         <v>8</v>
       </c>
       <c r="F156" s="8" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="G156" s="8"/>
       <c r="H156" s="8"/>
@@ -4868,7 +4862,7 @@
         <v>8</v>
       </c>
       <c r="F157" s="8" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="G157" s="8"/>
       <c r="H157" s="8"/>
@@ -4891,7 +4885,7 @@
         <v>8</v>
       </c>
       <c r="F158" s="8" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="G158" s="8"/>
       <c r="H158" s="8"/>
@@ -4902,10 +4896,10 @@
     </row>
     <row r="159" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B159" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C159" s="7" t="s">
         <v>18</v>
-      </c>
-      <c r="C159" s="7" t="s">
-        <v>19</v>
       </c>
       <c r="D159" s="8" t="n">
         <v>13</v>
@@ -4914,7 +4908,7 @@
         <v>8</v>
       </c>
       <c r="F159" s="8" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="G159" s="8"/>
       <c r="H159" s="8"/>
@@ -4937,7 +4931,7 @@
         <v>8</v>
       </c>
       <c r="F160" s="8" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="G160" s="8"/>
       <c r="H160" s="8"/>
@@ -4960,7 +4954,7 @@
         <v>8</v>
       </c>
       <c r="F161" s="8" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="G161" s="8"/>
       <c r="H161" s="8"/>
@@ -4983,7 +4977,7 @@
         <v>8</v>
       </c>
       <c r="F162" s="8" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="G162" s="8"/>
       <c r="H162" s="8"/>
@@ -4994,10 +4988,10 @@
     </row>
     <row r="163" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B163" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C163" s="7" t="s">
         <v>18</v>
-      </c>
-      <c r="C163" s="7" t="s">
-        <v>19</v>
       </c>
       <c r="D163" s="8" t="n">
         <v>14</v>
@@ -5006,7 +5000,7 @@
         <v>8</v>
       </c>
       <c r="F163" s="8" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G163" s="8"/>
       <c r="H163" s="8"/>
@@ -5029,7 +5023,7 @@
         <v>8</v>
       </c>
       <c r="F164" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G164" s="8"/>
       <c r="H164" s="8"/>
@@ -5052,7 +5046,7 @@
         <v>8</v>
       </c>
       <c r="F165" s="8" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="G165" s="8"/>
       <c r="H165" s="8"/>
@@ -5075,7 +5069,7 @@
         <v>8</v>
       </c>
       <c r="F166" s="8" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="G166" s="8"/>
       <c r="H166" s="8"/>
@@ -5086,10 +5080,10 @@
     </row>
     <row r="167" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B167" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C167" s="7" t="s">
         <v>18</v>
-      </c>
-      <c r="C167" s="7" t="s">
-        <v>19</v>
       </c>
       <c r="D167" s="8" t="n">
         <v>20</v>
@@ -5098,7 +5092,7 @@
         <v>8</v>
       </c>
       <c r="F167" s="8" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="G167" s="8"/>
       <c r="H167" s="8"/>
@@ -5121,13 +5115,13 @@
         <v>8</v>
       </c>
       <c r="F168" s="8" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="G168" s="8"/>
       <c r="H168" s="8"/>
       <c r="I168" s="8"/>
       <c r="J168" s="8" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="169" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5144,7 +5138,7 @@
         <v>8</v>
       </c>
       <c r="F169" s="8" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="G169" s="8"/>
       <c r="H169" s="8"/>
@@ -5167,7 +5161,7 @@
         <v>8</v>
       </c>
       <c r="F170" s="8" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="G170" s="8"/>
       <c r="H170" s="8"/>
@@ -5178,10 +5172,10 @@
     </row>
     <row r="171" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B171" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C171" s="7" t="s">
         <v>18</v>
-      </c>
-      <c r="C171" s="7" t="s">
-        <v>19</v>
       </c>
       <c r="D171" s="8" t="n">
         <v>21</v>
@@ -5190,13 +5184,13 @@
         <v>8</v>
       </c>
       <c r="F171" s="8" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G171" s="8"/>
       <c r="H171" s="8"/>
       <c r="I171" s="8"/>
       <c r="J171" s="8" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
     </row>
     <row r="172" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5213,13 +5207,13 @@
         <v>8</v>
       </c>
       <c r="F172" s="8" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="G172" s="8"/>
       <c r="H172" s="8"/>
       <c r="I172" s="8"/>
       <c r="J172" s="8" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="173" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5236,7 +5230,7 @@
         <v>8</v>
       </c>
       <c r="F173" s="8" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="G173" s="8"/>
       <c r="H173" s="8"/>
@@ -5259,7 +5253,7 @@
         <v>8</v>
       </c>
       <c r="F174" s="8" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="G174" s="8"/>
       <c r="H174" s="8"/>
@@ -5270,10 +5264,10 @@
     </row>
     <row r="175" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B175" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C175" s="7" t="s">
         <v>18</v>
-      </c>
-      <c r="C175" s="7" t="s">
-        <v>19</v>
       </c>
       <c r="D175" s="8" t="n">
         <v>27</v>
@@ -5282,7 +5276,7 @@
         <v>8</v>
       </c>
       <c r="F175" s="8" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="G175" s="8"/>
       <c r="H175" s="8"/>
@@ -5305,7 +5299,7 @@
         <v>8</v>
       </c>
       <c r="F176" s="8" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="G176" s="8"/>
       <c r="H176" s="8"/>
@@ -5328,7 +5322,7 @@
         <v>8</v>
       </c>
       <c r="F177" s="8" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="G177" s="8"/>
       <c r="H177" s="8"/>
@@ -5351,7 +5345,7 @@
         <v>8</v>
       </c>
       <c r="F178" s="8" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="G178" s="8"/>
       <c r="H178" s="8"/>
@@ -5362,10 +5356,10 @@
     </row>
     <row r="179" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B179" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C179" s="7" t="s">
         <v>18</v>
-      </c>
-      <c r="C179" s="7" t="s">
-        <v>19</v>
       </c>
       <c r="D179" s="8" t="n">
         <v>28</v>
@@ -5374,7 +5368,7 @@
         <v>8</v>
       </c>
       <c r="F179" s="8" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="G179" s="8"/>
       <c r="H179" s="8"/>
@@ -5397,13 +5391,13 @@
         <v>9</v>
       </c>
       <c r="F180" s="8" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="G180" s="8"/>
       <c r="H180" s="8"/>
       <c r="I180" s="8"/>
       <c r="J180" s="8" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
     </row>
     <row r="181" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5420,7 +5414,7 @@
         <v>9</v>
       </c>
       <c r="F181" s="8" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="G181" s="8"/>
       <c r="H181" s="8"/>
@@ -5443,7 +5437,7 @@
         <v>9</v>
       </c>
       <c r="F182" s="8" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="G182" s="8"/>
       <c r="H182" s="8"/>
@@ -5454,10 +5448,10 @@
     </row>
     <row r="183" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B183" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C183" s="7" t="s">
         <v>18</v>
-      </c>
-      <c r="C183" s="7" t="s">
-        <v>19</v>
       </c>
       <c r="D183" s="8" t="n">
         <v>3</v>
@@ -5466,7 +5460,7 @@
         <v>9</v>
       </c>
       <c r="F183" s="8" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G183" s="8"/>
       <c r="H183" s="8"/>
@@ -5489,7 +5483,7 @@
         <v>9</v>
       </c>
       <c r="F184" s="8" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="G184" s="8"/>
       <c r="H184" s="8"/>
@@ -5512,7 +5506,7 @@
         <v>9</v>
       </c>
       <c r="F185" s="8" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="G185" s="8"/>
       <c r="H185" s="8"/>
@@ -5535,7 +5529,7 @@
         <v>9</v>
       </c>
       <c r="F186" s="8" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G186" s="8"/>
       <c r="H186" s="8"/>
@@ -5546,10 +5540,10 @@
     </row>
     <row r="187" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B187" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C187" s="7" t="s">
         <v>18</v>
-      </c>
-      <c r="C187" s="7" t="s">
-        <v>19</v>
       </c>
       <c r="D187" s="8" t="n">
         <v>4</v>
@@ -5558,7 +5552,7 @@
         <v>9</v>
       </c>
       <c r="F187" s="8" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="G187" s="8"/>
       <c r="H187" s="8"/>
@@ -5581,7 +5575,7 @@
         <v>9</v>
       </c>
       <c r="F188" s="8" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="G188" s="8"/>
       <c r="H188" s="8"/>
@@ -5604,7 +5598,7 @@
         <v>9</v>
       </c>
       <c r="F189" s="8" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="G189" s="8"/>
       <c r="H189" s="8"/>
@@ -5627,7 +5621,7 @@
         <v>9</v>
       </c>
       <c r="F190" s="8" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G190" s="8"/>
       <c r="H190" s="8"/>
@@ -5638,10 +5632,10 @@
     </row>
     <row r="191" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B191" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C191" s="7" t="s">
         <v>18</v>
-      </c>
-      <c r="C191" s="7" t="s">
-        <v>19</v>
       </c>
       <c r="D191" s="8" t="n">
         <v>10</v>
@@ -5650,7 +5644,7 @@
         <v>9</v>
       </c>
       <c r="F191" s="8" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="G191" s="8"/>
       <c r="H191" s="8"/>
@@ -5673,13 +5667,13 @@
         <v>9</v>
       </c>
       <c r="F192" s="8" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="G192" s="8"/>
       <c r="H192" s="8"/>
       <c r="I192" s="8"/>
       <c r="J192" s="8" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="193" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5696,7 +5690,7 @@
         <v>9</v>
       </c>
       <c r="F193" s="8" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="G193" s="8"/>
       <c r="H193" s="8"/>
@@ -5719,7 +5713,7 @@
         <v>9</v>
       </c>
       <c r="F194" s="8" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="G194" s="8"/>
       <c r="H194" s="8"/>
@@ -5730,10 +5724,10 @@
     </row>
     <row r="195" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B195" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C195" s="7" t="s">
         <v>18</v>
-      </c>
-      <c r="C195" s="7" t="s">
-        <v>19</v>
       </c>
       <c r="D195" s="8" t="n">
         <v>11</v>
@@ -5742,7 +5736,7 @@
         <v>9</v>
       </c>
       <c r="F195" s="8" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="G195" s="8"/>
       <c r="H195" s="8"/>
@@ -5765,7 +5759,7 @@
         <v>9</v>
       </c>
       <c r="F196" s="8" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="G196" s="8"/>
       <c r="H196" s="8"/>
@@ -5788,7 +5782,7 @@
         <v>9</v>
       </c>
       <c r="F197" s="8" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="G197" s="8"/>
       <c r="H197" s="8"/>
@@ -5811,7 +5805,7 @@
         <v>9</v>
       </c>
       <c r="F198" s="8" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="G198" s="8"/>
       <c r="H198" s="8"/>
@@ -5822,10 +5816,10 @@
     </row>
     <row r="199" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B199" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C199" s="7" t="s">
         <v>18</v>
-      </c>
-      <c r="C199" s="7" t="s">
-        <v>19</v>
       </c>
       <c r="D199" s="8" t="n">
         <v>17</v>
@@ -5834,7 +5828,7 @@
         <v>9</v>
       </c>
       <c r="F199" s="8" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="G199" s="8"/>
       <c r="H199" s="8"/>
@@ -5857,7 +5851,7 @@
         <v>9</v>
       </c>
       <c r="F200" s="8" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="G200" s="8"/>
       <c r="H200" s="8"/>
@@ -5880,13 +5874,13 @@
         <v>9</v>
       </c>
       <c r="F201" s="8" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="G201" s="8"/>
       <c r="H201" s="8"/>
       <c r="I201" s="8"/>
       <c r="J201" s="8" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="202" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5903,7 +5897,7 @@
         <v>9</v>
       </c>
       <c r="F202" s="8" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G202" s="8"/>
       <c r="H202" s="8"/>
@@ -5914,10 +5908,10 @@
     </row>
     <row r="203" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B203" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C203" s="7" t="s">
         <v>18</v>
-      </c>
-      <c r="C203" s="7" t="s">
-        <v>19</v>
       </c>
       <c r="D203" s="8" t="n">
         <v>18</v>
@@ -5926,7 +5920,7 @@
         <v>9</v>
       </c>
       <c r="F203" s="8" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="G203" s="8"/>
       <c r="H203" s="8"/>
@@ -5949,7 +5943,7 @@
         <v>9</v>
       </c>
       <c r="F204" s="8" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="G204" s="8"/>
       <c r="H204" s="8"/>
@@ -5972,13 +5966,13 @@
         <v>9</v>
       </c>
       <c r="F205" s="8" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="G205" s="8"/>
       <c r="H205" s="8"/>
       <c r="I205" s="8"/>
       <c r="J205" s="8" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="206" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5995,21 +5989,21 @@
         <v>9</v>
       </c>
       <c r="F206" s="8" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="G206" s="8"/>
       <c r="H206" s="8"/>
       <c r="I206" s="8"/>
       <c r="J206" s="8" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
     </row>
     <row r="207" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B207" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C207" s="7" t="s">
         <v>18</v>
-      </c>
-      <c r="C207" s="7" t="s">
-        <v>19</v>
       </c>
       <c r="D207" s="8" t="n">
         <v>24</v>
@@ -6018,7 +6012,7 @@
         <v>9</v>
       </c>
       <c r="F207" s="8" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="G207" s="8"/>
       <c r="H207" s="8"/>
@@ -6041,7 +6035,7 @@
         <v>9</v>
       </c>
       <c r="F208" s="8" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="G208" s="8"/>
       <c r="H208" s="8"/>
@@ -6064,7 +6058,7 @@
         <v>9</v>
       </c>
       <c r="F209" s="8" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="G209" s="8"/>
       <c r="H209" s="8"/>
@@ -6087,7 +6081,7 @@
         <v>9</v>
       </c>
       <c r="F210" s="8" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="G210" s="8"/>
       <c r="H210" s="8"/>
@@ -6098,10 +6092,10 @@
     </row>
     <row r="211" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B211" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C211" s="7" t="s">
         <v>18</v>
-      </c>
-      <c r="C211" s="7" t="s">
-        <v>19</v>
       </c>
       <c r="D211" s="8" t="n">
         <v>25</v>
@@ -6110,7 +6104,7 @@
         <v>9</v>
       </c>
       <c r="F211" s="8" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="G211" s="8"/>
       <c r="H211" s="8"/>
@@ -6133,13 +6127,13 @@
         <v>10</v>
       </c>
       <c r="F212" s="8" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="G212" s="8"/>
       <c r="H212" s="8"/>
       <c r="I212" s="8"/>
       <c r="J212" s="8" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="213" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6156,7 +6150,7 @@
         <v>10</v>
       </c>
       <c r="F213" s="8" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="G213" s="8"/>
       <c r="H213" s="8"/>
@@ -6179,7 +6173,7 @@
         <v>10</v>
       </c>
       <c r="F214" s="8" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="G214" s="8"/>
       <c r="H214" s="8"/>
@@ -6190,10 +6184,10 @@
     </row>
     <row r="215" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B215" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C215" s="7" t="s">
         <v>18</v>
-      </c>
-      <c r="C215" s="7" t="s">
-        <v>19</v>
       </c>
       <c r="D215" s="8" t="n">
         <v>1</v>
@@ -6202,7 +6196,7 @@
         <v>10</v>
       </c>
       <c r="F215" s="8" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="G215" s="8"/>
       <c r="H215" s="8"/>
@@ -6225,13 +6219,13 @@
         <v>10</v>
       </c>
       <c r="F216" s="8" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="G216" s="8"/>
       <c r="H216" s="8"/>
       <c r="I216" s="8"/>
       <c r="J216" s="8" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="217" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6248,7 +6242,7 @@
         <v>10</v>
       </c>
       <c r="F217" s="8" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="G217" s="8"/>
       <c r="H217" s="8"/>
@@ -6271,21 +6265,21 @@
         <v>10</v>
       </c>
       <c r="F218" s="8" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="G218" s="8"/>
       <c r="H218" s="8"/>
       <c r="I218" s="8"/>
       <c r="J218" s="8" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
     </row>
     <row r="219" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B219" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C219" s="7" t="s">
         <v>18</v>
-      </c>
-      <c r="C219" s="7" t="s">
-        <v>19</v>
       </c>
       <c r="D219" s="8" t="n">
         <v>2</v>
@@ -6294,7 +6288,7 @@
         <v>10</v>
       </c>
       <c r="F219" s="8" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="G219" s="8"/>
       <c r="H219" s="8"/>
@@ -6317,7 +6311,7 @@
         <v>10</v>
       </c>
       <c r="F220" s="8" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="G220" s="8"/>
       <c r="H220" s="8"/>
@@ -6340,7 +6334,7 @@
         <v>10</v>
       </c>
       <c r="F221" s="8" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G221" s="8"/>
       <c r="H221" s="8"/>
@@ -6363,7 +6357,7 @@
         <v>10</v>
       </c>
       <c r="F222" s="8" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="G222" s="8"/>
       <c r="H222" s="8"/>
@@ -6374,11 +6368,11 @@
     </row>
     <row r="223" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B223" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C223" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C223" s="7" t="s">
-        <v>19</v>
-      </c>
       <c r="D223" s="8" t="n">
         <v>8</v>
       </c>
@@ -6386,13 +6380,13 @@
         <v>10</v>
       </c>
       <c r="F223" s="8" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="G223" s="8"/>
       <c r="H223" s="8"/>
       <c r="I223" s="8"/>
       <c r="J223" s="8" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="224" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6409,7 +6403,7 @@
         <v>10</v>
       </c>
       <c r="F224" s="8" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="G224" s="8"/>
       <c r="H224" s="8"/>
@@ -6432,7 +6426,7 @@
         <v>10</v>
       </c>
       <c r="F225" s="8" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="G225" s="8"/>
       <c r="H225" s="8"/>
@@ -6455,7 +6449,7 @@
         <v>10</v>
       </c>
       <c r="F226" s="8" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="G226" s="8"/>
       <c r="H226" s="8"/>
@@ -6466,10 +6460,10 @@
     </row>
     <row r="227" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B227" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C227" s="7" t="s">
         <v>18</v>
-      </c>
-      <c r="C227" s="7" t="s">
-        <v>19</v>
       </c>
       <c r="D227" s="8" t="n">
         <v>9</v>
@@ -6478,13 +6472,13 @@
         <v>10</v>
       </c>
       <c r="F227" s="8" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="G227" s="8"/>
       <c r="H227" s="8"/>
       <c r="I227" s="8"/>
       <c r="J227" s="8" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
